--- a/outputs/Что можно продать оптом.xlsx
+++ b/outputs/Что можно продать оптом.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -751,17 +751,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea] / Охлаждающие гидрогелевые патчи для глаз с экстрактом агавы</t>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>360</v>
+        <v>455</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>499</v>
+        <v>292</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>179640</v>
+        <v>132860</v>
       </c>
     </row>
     <row r="17">
@@ -770,17 +770,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с коллагеном и коэнзимом Q10</t>
+          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>463</v>
+        <v>221</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>166680</v>
+        <v>76024</v>
       </c>
     </row>
     <row r="18">
@@ -789,17 +789,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
+          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>455</v>
+        <v>260</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>292</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>132860</v>
+        <v>75920</v>
       </c>
     </row>
     <row r="19">
@@ -808,17 +808,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>180</v>
+        <v>285</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>585</v>
+        <v>220</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>105300</v>
+        <v>62700</v>
       </c>
     </row>
     <row r="20">
@@ -827,17 +827,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea] / Смягчающие гидрогелевые патчи для глаз с экстрактом артишока</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>156</v>
+        <v>535</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>499</v>
+        <v>117</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>77844</v>
+        <v>62595</v>
       </c>
     </row>
     <row r="21">
@@ -846,17 +846,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>344</v>
+        <v>260</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>76024</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="22">
@@ -865,17 +865,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
+          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>260</v>
+        <v>60</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>292</v>
+        <v>951</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>75920</v>
+        <v>57060</v>
       </c>
     </row>
     <row r="23">
@@ -884,17 +884,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
+          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>117</v>
+        <v>200</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>585</v>
+        <v>220</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>68445</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="24">
@@ -903,17 +903,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>89</v>
+        <v>325</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>710</v>
+        <v>130</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>63190</v>
+        <v>42250</v>
       </c>
     </row>
     <row r="25">
@@ -922,17 +922,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>285</v>
+        <v>25</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>220</v>
+        <v>1269</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>62700</v>
+        <v>31725</v>
       </c>
     </row>
     <row r="26">
@@ -941,17 +941,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>535</v>
+        <v>31</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>117</v>
+        <v>1015</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>62595</v>
+        <v>31465</v>
       </c>
     </row>
     <row r="27">
@@ -960,17 +960,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JMSOLUTION PANTHELENE INTENSIVE BARRIER MASK</t>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>541</v>
+        <v>814</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>59510</v>
+        <v>28490</v>
       </c>
     </row>
     <row r="28">
@@ -979,17 +979,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JMSOLUTION GLORY AQUA FULLERENE MASK DELUXE</t>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>541</v>
+        <v>442</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>59510</v>
+        <v>13260</v>
       </c>
     </row>
     <row r="29">
@@ -998,317 +998,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Water Luminous S.O.S. Ringer Mask Black [35ml*10ea] / Ультраувлажняющая тканевая маска</t>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>541</v>
+        <v>194</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>59510</v>
+        <v>11640</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>260</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>220</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>57200</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>951</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>57060</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea] / гидрогелевые патчи для глаз с золотом</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>548</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>49320</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>JMSOLUTION - Active Jellyfish Vital Mask [30ml*10ea] / Ультратонкая тканевая маска с экстрактом медузы</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>411</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>45210</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>JMSOLUTION GREEN DEAR TIGER CICA MASK PURE 30ml*10ea / Регенерирующая маска для лица с центеллой</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>411</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>45210</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>JMSOLUTION ACTIVE BLACK CAVIAR MASK [30ml*10ea] / Ультратонкая тканевая маска с черной икрой</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>411</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>45210</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>JMSOLUTION - Active Golden Caviar Nourishing Mask [30ml*10ea] / Ультратонкая тканевая маска с золотом и икрой</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>411</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>45210</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>220</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>44000</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>325</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>42250</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>JMSOLUTION - The Natural Cordyceps Melitaris Mask Moisture [30ml*10ea] / Тканевая маска для лица с экстрактом кордицепса и комплексом аминокислот</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>383</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>42130</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>1269</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>31725</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>1015</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>31465</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>814</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>28490</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>442</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>13260</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>194</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>11640</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr"/>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr"/>
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
-        <v>40756</v>
-      </c>
-      <c r="D45" s="6" t="inlineStr"/>
-      <c r="E45" s="5" t="n">
-        <v>22952941</v>
+      <c r="C30" s="5" t="n">
+        <v>38524</v>
+      </c>
+      <c r="D30" s="6" t="inlineStr"/>
+      <c r="E30" s="5" t="n">
+        <v>21841022</v>
       </c>
     </row>
   </sheetData>
@@ -1322,7 +1037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1917,33 +1632,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea] / Охлаждающие гидрогелевые патчи для глаз с экстрактом агавы</t>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>360</v>
+        <v>800</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>360</v>
+        <v>455</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>345</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
       <c r="I16" s="3" t="n">
-        <v>499</v>
+        <v>292</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>179640</v>
+        <v>132860</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>15118</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17">
@@ -1952,11 +1669,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с коллагеном и коэнзимом Q10</t>
+          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0</v>
@@ -1965,20 +1682,20 @@
         <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" s="3" t="n">
-        <v>463</v>
+        <v>221</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>166680</v>
+        <v>76024</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>14200</v>
+        <v>6444</v>
       </c>
     </row>
     <row r="18">
@@ -1987,7 +1704,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
+          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1997,13 +1714,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>455</v>
+        <v>260</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>345</v>
+        <v>540</v>
       </c>
       <c r="H18" t="n">
         <v>12</v>
@@ -2012,10 +1729,10 @@
         <v>292</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>132860</v>
+        <v>75920</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -2024,33 +1741,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>180</v>
+        <v>285</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12</v>
+      </c>
       <c r="I19" s="3" t="n">
-        <v>585</v>
+        <v>220</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>105300</v>
+        <v>62700</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>8935</v>
+        <v>5254</v>
       </c>
     </row>
     <row r="20">
@@ -2059,33 +1778,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea] / Смягчающие гидрогелевые патчи для глаз с экстрактом артишока</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>156</v>
+        <v>1000</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>156</v>
+        <v>535</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+        <v>465</v>
+      </c>
+      <c r="H20" t="n">
+        <v>12</v>
+      </c>
       <c r="I20" s="3" t="n">
-        <v>499</v>
+        <v>117</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>77844</v>
+        <v>62595</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>6551</v>
+        <v>5546</v>
       </c>
     </row>
     <row r="21">
@@ -2094,11 +1815,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>344</v>
+        <v>260</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0</v>
@@ -2107,20 +1828,20 @@
         <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>344</v>
+        <v>260</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" s="3" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>76024</v>
+        <v>57200</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>6444</v>
+        <v>4793</v>
       </c>
     </row>
     <row r="22">
@@ -2129,35 +1850,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
+          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>800</v>
+        <v>90</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>260</v>
+        <v>60</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>540</v>
+        <v>30</v>
       </c>
       <c r="H22" t="n">
         <v>12</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>292</v>
+        <v>951</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>75920</v>
+        <v>57060</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -2166,11 +1887,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
+          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>117</v>
+        <v>200</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0</v>
@@ -2179,20 +1900,20 @@
         <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>117</v>
+        <v>200</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" s="3" t="n">
-        <v>585</v>
+        <v>220</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>68445</v>
+        <v>44000</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>5808</v>
+        <v>3687</v>
       </c>
     </row>
     <row r="24">
@@ -2201,33 +1922,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>89</v>
+        <v>400</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>89</v>
+        <v>325</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>75</v>
+      </c>
+      <c r="H24" t="n">
+        <v>12</v>
+      </c>
       <c r="I24" s="3" t="n">
-        <v>710</v>
+        <v>130</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>63190</v>
+        <v>42250</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>5303</v>
+        <v>3586</v>
       </c>
     </row>
     <row r="25">
@@ -2236,35 +1959,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>300</v>
+        <v>55</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>285</v>
+        <v>25</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H25" t="n">
         <v>12</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>220</v>
+        <v>1269</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>62700</v>
+        <v>31725</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>5254</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="26">
@@ -2273,35 +1996,33 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>1000</v>
+        <v>31</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="F26" s="2" t="n">
-        <v>535</v>
-      </c>
       <c r="G26" s="2" t="n">
-        <v>465</v>
-      </c>
-      <c r="H26" t="n">
-        <v>12</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" s="3" t="n">
-        <v>117</v>
+        <v>1015</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>62595</v>
+        <v>31465</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>5546</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="27">
@@ -2310,33 +2031,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JMSOLUTION PANTHELENE INTENSIVE BARRIER MASK</t>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>110</v>
+        <v>650</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
+        <v>615</v>
+      </c>
+      <c r="H27" t="n">
+        <v>12</v>
+      </c>
       <c r="I27" s="3" t="n">
-        <v>541</v>
+        <v>814</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>59510</v>
+        <v>28490</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>5018</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2345,33 +2068,33 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JMSOLUTION GLORY AQUA FULLERENE MASK DELUXE</t>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" s="3" t="n">
-        <v>541</v>
+        <v>442</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>59510</v>
+        <v>13260</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>5018</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="29">
@@ -2380,601 +2103,66 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Water Luminous S.O.S. Ringer Mask Black [35ml*10ea] / Ультраувлажняющая тканевая маска</t>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
+        <v>240</v>
+      </c>
+      <c r="H29" t="n">
+        <v>12</v>
+      </c>
       <c r="I29" s="3" t="n">
-        <v>541</v>
+        <v>194</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>59510</v>
+        <v>11640</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>5018</v>
+        <v>983</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>260</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>260</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" s="3" t="n">
-        <v>220</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>57200</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>4793</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H31" t="n">
-        <v>12</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>951</v>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>57060</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea] / гидрогелевые патчи для глаз с золотом</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>405</v>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>315</v>
-      </c>
-      <c r="H32" t="n">
-        <v>12</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>548</v>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>49320</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>8189</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>JMSOLUTION - Active Jellyfish Vital Mask [30ml*10ea] / Ультратонкая тканевая маска с экстрактом медузы</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" s="3" t="n">
-        <v>411</v>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>45210</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>3795</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>JMSOLUTION GREEN DEAR TIGER CICA MASK PURE 30ml*10ea / Регенерирующая маска для лица с центеллой</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" s="3" t="n">
-        <v>411</v>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>45210</v>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>3795</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>JMSOLUTION ACTIVE BLACK CAVIAR MASK [30ml*10ea] / Ультратонкая тканевая маска с черной икрой</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" s="3" t="n">
-        <v>411</v>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>45210</v>
-      </c>
-      <c r="K35" s="2" t="n">
-        <v>3795</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>JMSOLUTION - Active Golden Caviar Nourishing Mask [30ml*10ea] / Ультратонкая тканевая маска с золотом и икрой</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" s="3" t="n">
-        <v>411</v>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>45210</v>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>3795</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" s="3" t="n">
-        <v>220</v>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>44000</v>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>3687</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>325</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="H38" t="n">
-        <v>12</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>42250</v>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>3586</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>JMSOLUTION - The Natural Cordyceps Melitaris Mask Moisture [30ml*10ea] / Тканевая маска для лица с экстрактом кордицепса и комплексом аминокислот</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" s="3" t="n">
-        <v>383</v>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>42130</v>
-      </c>
-      <c r="K39" s="2" t="n">
-        <v>3598</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H40" t="n">
-        <v>12</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>1269</v>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>31725</v>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>2652</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" s="3" t="n">
-        <v>1015</v>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>31465</v>
-      </c>
-      <c r="K41" s="2" t="n">
-        <v>2634</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>650</v>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>615</v>
-      </c>
-      <c r="H42" t="n">
-        <v>12</v>
-      </c>
-      <c r="I42" s="3" t="n">
-        <v>814</v>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>28490</v>
-      </c>
-      <c r="K42" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" s="3" t="n">
-        <v>442</v>
-      </c>
-      <c r="J43" s="2" t="n">
-        <v>13260</v>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>240</v>
-      </c>
-      <c r="H44" t="n">
-        <v>12</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>194</v>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>11640</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr"/>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr"/>
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
-        <v>56011</v>
-      </c>
-      <c r="D45" s="5" t="n">
+      <c r="C30" s="5" t="n">
+        <v>53464</v>
+      </c>
+      <c r="D30" s="5" t="n">
         <v>66888</v>
       </c>
-      <c r="E45" s="5" t="n">
-        <v>4420</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>40756</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>15255</v>
-      </c>
-      <c r="H45" s="4" t="inlineStr"/>
-      <c r="I45" s="6" t="inlineStr"/>
-      <c r="J45" s="5" t="n">
-        <v>22952941</v>
-      </c>
-      <c r="K45" s="5" t="n">
-        <v>1577061</v>
+      <c r="E30" s="5" t="n">
+        <v>4399</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>38524</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>14940</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="6" t="inlineStr"/>
+      <c r="J30" s="5" t="n">
+        <v>21841022</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>1479125</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Что можно продать оптом.xlsx
+++ b/outputs/Что можно продать оптом.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -618,17 +618,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1120</v>
+        <v>3670</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>612</v>
+        <v>194</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>685440</v>
+        <v>711980</v>
       </c>
     </row>
     <row r="10">
@@ -637,17 +637,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и пробиотиками</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>524</v>
+        <v>1120</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1197</v>
+        <v>612</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>627228</v>
+        <v>685440</v>
       </c>
     </row>
     <row r="11">
@@ -656,17 +656,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
+          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и пробиотиками</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>966</v>
+        <v>524</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>626</v>
+        <v>1197</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>604716</v>
+        <v>627228</v>
       </c>
     </row>
     <row r="12">
@@ -675,17 +675,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
+          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>397</v>
+        <v>966</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1191</v>
+        <v>626</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>472827</v>
+        <v>604716</v>
       </c>
     </row>
     <row r="13">
@@ -694,17 +694,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
+          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>335</v>
+        <v>397</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1080</v>
+        <v>1191</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>361800</v>
+        <v>472827</v>
       </c>
     </row>
     <row r="14">
@@ -713,17 +713,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
+          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>779</v>
+        <v>1080</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>268755</v>
+        <v>361800</v>
       </c>
     </row>
     <row r="15">
@@ -732,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной крем с экстрактом ласточкиного гнезда</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>894</v>
+        <v>345</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>243</v>
+        <v>779</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>217242</v>
+        <v>268755</v>
       </c>
     </row>
     <row r="16">
@@ -751,17 +751,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
+          <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной крем с экстрактом ласточкиного гнезда</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>455</v>
+        <v>894</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>292</v>
+        <v>243</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>132860</v>
+        <v>217242</v>
       </c>
     </row>
     <row r="17">
@@ -770,17 +770,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>344</v>
+        <v>455</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>221</v>
+        <v>292</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>76024</v>
+        <v>132860</v>
       </c>
     </row>
     <row r="18">
@@ -789,17 +789,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
+          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>260</v>
+        <v>344</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>292</v>
+        <v>221</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>75920</v>
+        <v>76024</v>
       </c>
     </row>
     <row r="19">
@@ -808,17 +808,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
+          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>220</v>
+        <v>292</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>62700</v>
+        <v>75920</v>
       </c>
     </row>
     <row r="20">
@@ -827,17 +827,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>535</v>
+        <v>285</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>117</v>
+        <v>220</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>62595</v>
+        <v>62700</v>
       </c>
     </row>
     <row r="21">
@@ -846,17 +846,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>260</v>
+        <v>535</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>220</v>
+        <v>117</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>57200</v>
+        <v>62595</v>
       </c>
     </row>
     <row r="22">
@@ -865,17 +865,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>951</v>
+        <v>220</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>57060</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="23">
@@ -884,17 +884,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
+          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>220</v>
+        <v>951</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>44000</v>
+        <v>57060</v>
       </c>
     </row>
     <row r="24">
@@ -903,17 +903,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
+          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>42250</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="25">
@@ -922,17 +922,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1269</v>
+        <v>130</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>31725</v>
+        <v>42250</v>
       </c>
     </row>
     <row r="26">
@@ -941,17 +941,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1015</v>
+        <v>1269</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>31465</v>
+        <v>31725</v>
       </c>
     </row>
     <row r="27">
@@ -960,17 +960,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>814</v>
+        <v>1015</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>28490</v>
+        <v>31465</v>
       </c>
     </row>
     <row r="28">
@@ -979,17 +979,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>442</v>
+        <v>814</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>13260</v>
+        <v>28490</v>
       </c>
     </row>
     <row r="29">
@@ -998,32 +998,51 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>442</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>13260</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C30" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>194</v>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E30" s="2" t="n">
         <v>11640</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr"/>
-      <c r="B30" s="4" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr"/>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n">
-        <v>38524</v>
-      </c>
-      <c r="D30" s="6" t="inlineStr"/>
-      <c r="E30" s="5" t="n">
-        <v>21841022</v>
+      <c r="C31" s="5" t="n">
+        <v>42194</v>
+      </c>
+      <c r="D31" s="6" t="inlineStr"/>
+      <c r="E31" s="5" t="n">
+        <v>22553002</v>
       </c>
     </row>
   </sheetData>
@@ -1037,7 +1056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1375,35 +1394,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1375</v>
+        <v>7340</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>17</v>
+        <v>709</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1120</v>
+        <v>3670</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>255</v>
+        <v>3670</v>
       </c>
       <c r="H9" t="n">
-        <v>12</v>
+        <v>3.8</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>612</v>
+        <v>194</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>685440</v>
+        <v>711980</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>226</v>
+        <v>60812</v>
       </c>
     </row>
     <row r="10">
@@ -1412,35 +1431,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и пробиотиками</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>614</v>
+        <v>1375</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>524</v>
+        <v>1120</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>90</v>
+        <v>255</v>
       </c>
       <c r="H10" t="n">
         <v>12</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1197</v>
+        <v>612</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>627228</v>
+        <v>685440</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>52701</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11">
@@ -1449,35 +1468,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
+          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и пробиотиками</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>966</v>
+        <v>614</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>966</v>
+        <v>524</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H11" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>626</v>
+        <v>1197</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>604716</v>
+        <v>627228</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>89429</v>
+        <v>52701</v>
       </c>
     </row>
     <row r="12">
@@ -1486,33 +1505,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
+          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>397</v>
+        <v>966</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>397</v>
+        <v>966</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>36</v>
+      </c>
       <c r="I12" s="3" t="n">
-        <v>1191</v>
+        <v>626</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>472827</v>
+        <v>604716</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>47464</v>
+        <v>89429</v>
       </c>
     </row>
     <row r="13">
@@ -1521,35 +1542,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
+          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1355</v>
+        <v>397</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>335</v>
+        <v>397</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1020</v>
-      </c>
-      <c r="H13" t="n">
-        <v>12</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" s="3" t="n">
-        <v>1080</v>
+        <v>1191</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>361800</v>
+        <v>472827</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>30231</v>
+        <v>47464</v>
       </c>
     </row>
     <row r="14">
@@ -1558,35 +1577,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
+          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1500</v>
+        <v>1355</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1155</v>
+        <v>1020</v>
       </c>
       <c r="H14" t="n">
         <v>12</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>779</v>
+        <v>1080</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>268755</v>
+        <v>361800</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>115</v>
+        <v>30231</v>
       </c>
     </row>
     <row r="15">
@@ -1595,35 +1614,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной крем с экстрактом ласточкиного гнезда</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1614</v>
+        <v>1500</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>894</v>
+        <v>345</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>720</v>
+        <v>1155</v>
       </c>
       <c r="H15" t="n">
         <v>12</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>243</v>
+        <v>779</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>217242</v>
+        <v>268755</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>18330</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -1632,35 +1651,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
+          <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной крем с экстрактом ласточкиного гнезда</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>800</v>
+        <v>1614</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>455</v>
+        <v>894</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>345</v>
+        <v>720</v>
       </c>
       <c r="H16" t="n">
         <v>12</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>292</v>
+        <v>243</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>132860</v>
+        <v>217242</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>47</v>
+        <v>18330</v>
       </c>
     </row>
     <row r="17">
@@ -1669,33 +1688,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>344</v>
+        <v>800</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>344</v>
+        <v>455</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>345</v>
+      </c>
+      <c r="H17" t="n">
+        <v>12</v>
+      </c>
       <c r="I17" s="3" t="n">
-        <v>221</v>
+        <v>292</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>76024</v>
+        <v>132860</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>6444</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18">
@@ -1704,35 +1725,33 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
+          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>800</v>
+        <v>344</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>260</v>
+        <v>344</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>540</v>
-      </c>
-      <c r="H18" t="n">
-        <v>12</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" s="3" t="n">
-        <v>292</v>
+        <v>221</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>75920</v>
+        <v>76024</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>27</v>
+        <v>6444</v>
       </c>
     </row>
     <row r="19">
@@ -1741,35 +1760,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
+          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>15</v>
+        <v>540</v>
       </c>
       <c r="H19" t="n">
         <v>12</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>220</v>
+        <v>292</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>62700</v>
+        <v>75920</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>5254</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1778,35 +1797,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>535</v>
+        <v>285</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>465</v>
+        <v>15</v>
       </c>
       <c r="H20" t="n">
         <v>12</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>117</v>
+        <v>220</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>62595</v>
+        <v>62700</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>5546</v>
+        <v>5254</v>
       </c>
     </row>
     <row r="21">
@@ -1815,33 +1834,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>260</v>
+        <v>535</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>465</v>
+      </c>
+      <c r="H21" t="n">
+        <v>12</v>
+      </c>
       <c r="I21" s="3" t="n">
-        <v>220</v>
+        <v>117</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>57200</v>
+        <v>62595</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>4793</v>
+        <v>5546</v>
       </c>
     </row>
     <row r="22">
@@ -1850,35 +1871,33 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>90</v>
+        <v>260</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H22" t="n">
-        <v>12</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" s="3" t="n">
-        <v>951</v>
+        <v>220</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>57060</v>
+        <v>57200</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>29</v>
+        <v>4793</v>
       </c>
     </row>
     <row r="23">
@@ -1887,33 +1906,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
+          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="H23" t="n">
+        <v>12</v>
+      </c>
       <c r="I23" s="3" t="n">
-        <v>220</v>
+        <v>951</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>44000</v>
+        <v>57060</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>3687</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24">
@@ -1922,35 +1943,33 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
+          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="H24" t="n">
-        <v>12</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" s="3" t="n">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>42250</v>
+        <v>44000</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>3586</v>
+        <v>3687</v>
       </c>
     </row>
     <row r="25">
@@ -1959,35 +1978,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>55</v>
+        <v>400</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="H25" t="n">
         <v>12</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1269</v>
+        <v>130</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>31725</v>
+        <v>42250</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>2652</v>
+        <v>3586</v>
       </c>
     </row>
     <row r="26">
@@ -1996,33 +2015,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="H26" t="n">
+        <v>12</v>
+      </c>
       <c r="I26" s="3" t="n">
-        <v>1015</v>
+        <v>1269</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>31465</v>
+        <v>31725</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>2634</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="27">
@@ -2031,35 +2052,33 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>650</v>
+        <v>31</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>615</v>
-      </c>
-      <c r="H27" t="n">
-        <v>12</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" s="3" t="n">
-        <v>814</v>
+        <v>1015</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>28490</v>
+        <v>31465</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>3</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="28">
@@ -2068,33 +2087,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>30</v>
+        <v>650</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
+        <v>615</v>
+      </c>
+      <c r="H28" t="n">
+        <v>12</v>
+      </c>
       <c r="I28" s="3" t="n">
-        <v>442</v>
+        <v>814</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>13260</v>
+        <v>28490</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1120</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2103,66 +2124,101 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" s="3" t="n">
+        <v>442</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>13260</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C30" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="D29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="2" t="n">
+      <c r="D30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="F30" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="G30" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H30" t="n">
         <v>12</v>
       </c>
-      <c r="I29" s="3" t="n">
+      <c r="I30" s="3" t="n">
         <v>194</v>
       </c>
-      <c r="J29" s="2" t="n">
+      <c r="J30" s="2" t="n">
         <v>11640</v>
       </c>
-      <c r="K29" s="2" t="n">
+      <c r="K30" s="2" t="n">
         <v>983</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr"/>
-      <c r="B30" s="4" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr"/>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n">
-        <v>53464</v>
-      </c>
-      <c r="D30" s="5" t="n">
+      <c r="C31" s="5" t="n">
+        <v>60804</v>
+      </c>
+      <c r="D31" s="5" t="n">
         <v>66888</v>
       </c>
-      <c r="E30" s="5" t="n">
-        <v>4399</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>38524</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>14940</v>
-      </c>
-      <c r="H30" s="4" t="inlineStr"/>
-      <c r="I30" s="6" t="inlineStr"/>
-      <c r="J30" s="5" t="n">
-        <v>21841022</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>1479125</v>
+      <c r="E31" s="5" t="n">
+        <v>5108</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>42194</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>18610</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="6" t="inlineStr"/>
+      <c r="J31" s="5" t="n">
+        <v>22553002</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>1539937</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Что можно продать оптом.xlsx
+++ b/outputs/Что можно продать оптом.xlsx
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>220</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>62700</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="21">
@@ -1038,11 +1038,11 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>42194</v>
+        <v>42209</v>
       </c>
       <c r="D31" s="6" t="inlineStr"/>
       <c r="E31" s="5" t="n">
-        <v>22553002</v>
+        <v>22556302</v>
       </c>
     </row>
   </sheetData>
@@ -1810,22 +1810,22 @@
         <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>220</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>62700</v>
+        <v>66000</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>5254</v>
+        <v>5531</v>
       </c>
     </row>
     <row r="21">
@@ -2207,18 +2207,18 @@
         <v>5108</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>42194</v>
+        <v>42209</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>18610</v>
+        <v>18595</v>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="6" t="inlineStr"/>
       <c r="J31" s="5" t="n">
-        <v>22553002</v>
+        <v>22556302</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>1539937</v>
+        <v>1540214</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Что можно продать оптом.xlsx
+++ b/outputs/Что можно продать оптом.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -492,10 +492,10 @@
         <v>9073</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>644</v>
+        <v>620</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5843012</v>
+        <v>5625260</v>
       </c>
     </row>
     <row r="3">
@@ -511,10 +511,10 @@
         <v>7126</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>510</v>
+        <v>560</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3634260</v>
+        <v>3990560</v>
       </c>
     </row>
     <row r="4">
@@ -530,10 +530,10 @@
         <v>4520</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>731</v>
+        <v>803</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3304120</v>
+        <v>3629560</v>
       </c>
     </row>
     <row r="5">
@@ -549,10 +549,10 @@
         <v>4294</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1863596</v>
+        <v>1876478</v>
       </c>
     </row>
     <row r="6">
@@ -568,10 +568,10 @@
         <v>979</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1643</v>
+        <v>1616</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1608497</v>
+        <v>1582064</v>
       </c>
     </row>
     <row r="7">
@@ -587,10 +587,10 @@
         <v>3353</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>814779</v>
+        <v>821485</v>
       </c>
     </row>
     <row r="8">
@@ -606,10 +606,10 @@
         <v>1693</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>807561</v>
+        <v>812640</v>
       </c>
     </row>
     <row r="9">
@@ -618,17 +618,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3670</v>
+        <v>1120</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>194</v>
+        <v>673</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>711980</v>
+        <v>753760</v>
       </c>
     </row>
     <row r="10">
@@ -637,17 +637,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1120</v>
+        <v>3670</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>612</v>
+        <v>195</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>685440</v>
+        <v>715650</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         <v>524</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1197</v>
+        <v>1206</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>627228</v>
+        <v>631944</v>
       </c>
     </row>
     <row r="12">
@@ -682,10 +682,10 @@
         <v>966</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>626</v>
+        <v>587</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>604716</v>
+        <v>567042</v>
       </c>
     </row>
     <row r="13">
@@ -701,10 +701,10 @@
         <v>397</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1191</v>
+        <v>1179</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>472827</v>
+        <v>468063</v>
       </c>
     </row>
     <row r="14">
@@ -720,10 +720,10 @@
         <v>335</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1080</v>
+        <v>1089</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>361800</v>
+        <v>364815</v>
       </c>
     </row>
     <row r="15">
@@ -739,10 +739,10 @@
         <v>345</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>779</v>
+        <v>857</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>268755</v>
+        <v>295665</v>
       </c>
     </row>
     <row r="16">
@@ -758,10 +758,10 @@
         <v>894</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>217242</v>
+        <v>219030</v>
       </c>
     </row>
     <row r="17">
@@ -770,17 +770,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [1000ml]/ Шампунь с черным чесноком против выпадения волос</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>455</v>
+        <v>400</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>292</v>
+        <v>445</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>132860</v>
+        <v>178000</v>
       </c>
     </row>
     <row r="18">
@@ -789,17 +789,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
+          <t>DEOPROCE RINSE - BLACK GARLIC INTENSME ENERGY [1000ml] / Бальзам от выпадения волос Чёрный чеснок</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>344</v>
+        <v>400</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>221</v>
+        <v>434</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>76024</v>
+        <v>173600</v>
       </c>
     </row>
     <row r="19">
@@ -808,17 +808,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>260</v>
+        <v>455</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>292</v>
+        <v>321</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>75920</v>
+        <v>146055</v>
       </c>
     </row>
     <row r="20">
@@ -827,17 +827,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
+          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>220</v>
+        <v>321</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>66000</v>
+        <v>83460</v>
       </c>
     </row>
     <row r="21">
@@ -846,17 +846,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
+          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>535</v>
+        <v>344</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>117</v>
+        <v>222</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>62595</v>
+        <v>76368</v>
       </c>
     </row>
     <row r="22">
@@ -865,17 +865,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>57200</v>
+        <v>66600</v>
       </c>
     </row>
     <row r="23">
@@ -891,10 +891,10 @@
         <v>60</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>951</v>
+        <v>1046</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>57060</v>
+        <v>62760</v>
       </c>
     </row>
     <row r="24">
@@ -903,17 +903,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>200</v>
+        <v>535</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>220</v>
+        <v>117</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>44000</v>
+        <v>62595</v>
       </c>
     </row>
     <row r="25">
@@ -922,17 +922,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>325</v>
+        <v>260</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>130</v>
+        <v>222</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>42250</v>
+        <v>57720</v>
       </c>
     </row>
     <row r="26">
@@ -941,17 +941,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
+          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1269</v>
+        <v>222</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>31725</v>
+        <v>44400</v>
       </c>
     </row>
     <row r="27">
@@ -960,17 +960,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>31</v>
+        <v>325</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1015</v>
+        <v>131</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>31465</v>
+        <v>42575</v>
       </c>
     </row>
     <row r="28">
@@ -979,17 +979,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>814</v>
+        <v>1279</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>28490</v>
+        <v>31975</v>
       </c>
     </row>
     <row r="29">
@@ -998,17 +998,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>442</v>
+        <v>1023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>13260</v>
+        <v>31713</v>
       </c>
     </row>
     <row r="30">
@@ -1017,32 +1017,70 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>895</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>31325</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>445</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>13350</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
+      <c r="C32" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="D30" s="3" t="n">
-        <v>194</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>11640</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr"/>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="D32" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>11700</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr"/>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
-        <v>42209</v>
-      </c>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="5" t="n">
-        <v>22556302</v>
+      <c r="C33" s="5" t="n">
+        <v>43009</v>
+      </c>
+      <c r="D33" s="6" t="inlineStr"/>
+      <c r="E33" s="5" t="n">
+        <v>23468212</v>
       </c>
     </row>
   </sheetData>
@@ -1056,7 +1094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1157,13 +1195,13 @@
         <v>12</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>644</v>
+        <v>620</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>5843012</v>
+        <v>5625260</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>731302</v>
+        <v>513550</v>
       </c>
     </row>
     <row r="3">
@@ -1194,13 +1232,13 @@
         <v>14.9</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>510</v>
+        <v>560</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3634260</v>
+        <v>3990560</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>3499</v>
+        <v>359799</v>
       </c>
     </row>
     <row r="4">
@@ -1231,13 +1269,13 @@
         <v>15.6</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>731</v>
+        <v>803</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3304120</v>
+        <v>3629560</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>3408</v>
+        <v>328848</v>
       </c>
     </row>
     <row r="5">
@@ -1268,13 +1306,13 @@
         <v>12</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1863596</v>
+        <v>1876478</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>158307</v>
+        <v>171189</v>
       </c>
     </row>
     <row r="6">
@@ -1305,13 +1343,13 @@
         <v>12</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>1643</v>
+        <v>1616</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1608497</v>
+        <v>1582064</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>169812</v>
+        <v>143379</v>
       </c>
     </row>
     <row r="7">
@@ -1342,13 +1380,13 @@
         <v>12</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>814779</v>
+        <v>821485</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>68747</v>
+        <v>75453</v>
       </c>
     </row>
     <row r="8">
@@ -1379,13 +1417,13 @@
         <v>12</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>807561</v>
+        <v>812640</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>68749</v>
+        <v>73828</v>
       </c>
     </row>
     <row r="9">
@@ -1394,35 +1432,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>7340</v>
+        <v>1375</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>709</v>
+        <v>17</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>3670</v>
+        <v>1120</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>3670</v>
+        <v>255</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8</v>
+        <v>12</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>194</v>
+        <v>673</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>711980</v>
+        <v>753760</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>60812</v>
+        <v>68546</v>
       </c>
     </row>
     <row r="10">
@@ -1431,35 +1469,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1375</v>
+        <v>7340</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>17</v>
+        <v>709</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1120</v>
+        <v>3670</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>255</v>
+        <v>3670</v>
       </c>
       <c r="H10" t="n">
-        <v>12</v>
+        <v>3.8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>612</v>
+        <v>195</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>685440</v>
+        <v>715650</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>226</v>
+        <v>64482</v>
       </c>
     </row>
     <row r="11">
@@ -1490,13 +1528,13 @@
         <v>12</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1197</v>
+        <v>1206</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>627228</v>
+        <v>631944</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>52701</v>
+        <v>57417</v>
       </c>
     </row>
     <row r="12">
@@ -1527,13 +1565,13 @@
         <v>36</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>626</v>
+        <v>587</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>604716</v>
+        <v>567042</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>89429</v>
+        <v>51755</v>
       </c>
     </row>
     <row r="13">
@@ -1562,13 +1600,13 @@
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" s="3" t="n">
-        <v>1191</v>
+        <v>1179</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>472827</v>
+        <v>468063</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>47464</v>
+        <v>42700</v>
       </c>
     </row>
     <row r="14">
@@ -1599,13 +1637,13 @@
         <v>12</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1080</v>
+        <v>1089</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>361800</v>
+        <v>364815</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>30231</v>
+        <v>33246</v>
       </c>
     </row>
     <row r="15">
@@ -1636,13 +1674,13 @@
         <v>12</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>779</v>
+        <v>857</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>268755</v>
+        <v>295665</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>115</v>
+        <v>27025</v>
       </c>
     </row>
     <row r="16">
@@ -1673,13 +1711,13 @@
         <v>12</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>217242</v>
+        <v>219030</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>18330</v>
+        <v>20118</v>
       </c>
     </row>
     <row r="17">
@@ -1688,35 +1726,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [1000ml]/ Шампунь с черным чесноком против выпадения волос</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>455</v>
+        <v>400</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>345</v>
-      </c>
-      <c r="H17" t="n">
-        <v>12</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" s="3" t="n">
-        <v>292</v>
+        <v>445</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>132860</v>
+        <v>178000</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>47</v>
+        <v>16115</v>
       </c>
     </row>
     <row r="18">
@@ -1725,11 +1761,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
+          <t>DEOPROCE RINSE - BLACK GARLIC INTENSME ENERGY [1000ml] / Бальзам от выпадения волос Чёрный чеснок</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>344</v>
+        <v>400</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0</v>
@@ -1738,20 +1774,20 @@
         <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>344</v>
+        <v>400</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" s="3" t="n">
-        <v>221</v>
+        <v>434</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>76024</v>
+        <v>173600</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>6444</v>
+        <v>15671</v>
       </c>
     </row>
     <row r="19">
@@ -1760,7 +1796,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1770,25 +1806,25 @@
         <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>260</v>
+        <v>455</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>540</v>
+        <v>345</v>
       </c>
       <c r="H19" t="n">
         <v>12</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>292</v>
+        <v>321</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>75920</v>
+        <v>146055</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>27</v>
+        <v>13242</v>
       </c>
     </row>
     <row r="20">
@@ -1797,35 +1833,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
+          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>220</v>
+        <v>321</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>66000</v>
+        <v>83460</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>5531</v>
+        <v>7567</v>
       </c>
     </row>
     <row r="21">
@@ -1834,35 +1870,33 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
+          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1000</v>
+        <v>344</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>535</v>
+        <v>344</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>465</v>
-      </c>
-      <c r="H21" t="n">
-        <v>12</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" s="3" t="n">
-        <v>117</v>
+        <v>222</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>62595</v>
+        <v>76368</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>5546</v>
+        <v>6788</v>
       </c>
     </row>
     <row r="22">
@@ -1871,33 +1905,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
       <c r="I22" s="3" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>57200</v>
+        <v>66600</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>4793</v>
+        <v>6131</v>
       </c>
     </row>
     <row r="23">
@@ -1928,13 +1964,13 @@
         <v>12</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>951</v>
+        <v>1046</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>57060</v>
+        <v>62760</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>29</v>
+        <v>5729</v>
       </c>
     </row>
     <row r="24">
@@ -1943,33 +1979,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>200</v>
+        <v>535</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>465</v>
+      </c>
+      <c r="H24" t="n">
+        <v>12</v>
+      </c>
       <c r="I24" s="3" t="n">
-        <v>220</v>
+        <v>117</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>44000</v>
+        <v>62595</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>3687</v>
+        <v>5546</v>
       </c>
     </row>
     <row r="25">
@@ -1978,35 +2016,33 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>400</v>
+        <v>260</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>325</v>
+        <v>260</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="H25" t="n">
-        <v>12</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" s="3" t="n">
-        <v>130</v>
+        <v>222</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>42250</v>
+        <v>57720</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>3586</v>
+        <v>5313</v>
       </c>
     </row>
     <row r="26">
@@ -2015,35 +2051,33 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
+          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H26" t="n">
-        <v>12</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" s="3" t="n">
-        <v>1269</v>
+        <v>222</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>31725</v>
+        <v>44400</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>2652</v>
+        <v>4087</v>
       </c>
     </row>
     <row r="27">
@@ -2052,33 +2086,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>31</v>
+        <v>400</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>31</v>
+        <v>325</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
+        <v>75</v>
+      </c>
+      <c r="H27" t="n">
+        <v>12</v>
+      </c>
       <c r="I27" s="3" t="n">
-        <v>1015</v>
+        <v>131</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>31465</v>
+        <v>42575</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>2634</v>
+        <v>3911</v>
       </c>
     </row>
     <row r="28">
@@ -2087,35 +2123,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>650</v>
+        <v>55</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>615</v>
+        <v>30</v>
       </c>
       <c r="H28" t="n">
         <v>12</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>814</v>
+        <v>1279</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>28490</v>
+        <v>31975</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>3</v>
+        <v>2902</v>
       </c>
     </row>
     <row r="29">
@@ -2124,33 +2160,33 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" s="3" t="n">
-        <v>442</v>
+        <v>1023</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>13260</v>
+        <v>31713</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>1120</v>
+        <v>2882</v>
       </c>
     </row>
     <row r="30">
@@ -2159,66 +2195,138 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>300</v>
+        <v>650</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>240</v>
+        <v>615</v>
       </c>
       <c r="H30" t="n">
         <v>12</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>194</v>
+        <v>895</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>11640</v>
+        <v>31325</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>983</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr"/>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" s="3" t="n">
+        <v>445</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>13350</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="H32" t="n">
+        <v>12</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>11700</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr"/>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
-        <v>60804</v>
-      </c>
-      <c r="D31" s="5" t="n">
+      <c r="C33" s="5" t="n">
+        <v>61604</v>
+      </c>
+      <c r="D33" s="5" t="n">
         <v>66888</v>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E33" s="5" t="n">
         <v>5108</v>
       </c>
-      <c r="F31" s="5" t="n">
-        <v>42209</v>
-      </c>
-      <c r="G31" s="5" t="n">
+      <c r="F33" s="5" t="n">
+        <v>43009</v>
+      </c>
+      <c r="G33" s="5" t="n">
         <v>18595</v>
       </c>
-      <c r="H31" s="4" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="5" t="n">
-        <v>22556302</v>
-      </c>
-      <c r="K31" s="5" t="n">
-        <v>1540214</v>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="6" t="inlineStr"/>
+      <c r="J33" s="5" t="n">
+        <v>23468212</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>2132310</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Что можно продать оптом.xlsx
+++ b/outputs/Что можно продать оптом.xlsx
@@ -492,10 +492,10 @@
         <v>9073</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>620</v>
+        <v>563</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5625260</v>
+        <v>5108099</v>
       </c>
     </row>
     <row r="3">
@@ -511,10 +511,10 @@
         <v>7126</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>560</v>
+        <v>510</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3990560</v>
+        <v>3634260</v>
       </c>
     </row>
     <row r="4">
@@ -530,10 +530,10 @@
         <v>4520</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>803</v>
+        <v>730</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3629560</v>
+        <v>3299600</v>
       </c>
     </row>
     <row r="5">
@@ -549,10 +549,10 @@
         <v>4294</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>437</v>
+        <v>397</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1876478</v>
+        <v>1704718</v>
       </c>
     </row>
     <row r="6">
@@ -568,10 +568,10 @@
         <v>979</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1616</v>
+        <v>1470</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1582064</v>
+        <v>1439130</v>
       </c>
     </row>
     <row r="7">
@@ -587,10 +587,10 @@
         <v>3353</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>821485</v>
+        <v>744366</v>
       </c>
     </row>
     <row r="8">
@@ -606,10 +606,10 @@
         <v>1693</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>812640</v>
+        <v>738148</v>
       </c>
     </row>
     <row r="9">
@@ -625,10 +625,10 @@
         <v>1120</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>673</v>
+        <v>612</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>753760</v>
+        <v>685440</v>
       </c>
     </row>
     <row r="10">
@@ -644,10 +644,10 @@
         <v>3670</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>715650</v>
+        <v>649590</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         <v>524</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1206</v>
+        <v>1096</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>631944</v>
+        <v>574304</v>
       </c>
     </row>
     <row r="12">
@@ -682,10 +682,10 @@
         <v>966</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>587</v>
+        <v>533</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>567042</v>
+        <v>514878</v>
       </c>
     </row>
     <row r="13">
@@ -701,10 +701,10 @@
         <v>397</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1179</v>
+        <v>1071</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>468063</v>
+        <v>425187</v>
       </c>
     </row>
     <row r="14">
@@ -720,10 +720,10 @@
         <v>335</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1089</v>
+        <v>990</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>364815</v>
+        <v>331650</v>
       </c>
     </row>
     <row r="15">
@@ -739,10 +739,10 @@
         <v>345</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>857</v>
+        <v>779</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>295665</v>
+        <v>268755</v>
       </c>
     </row>
     <row r="16">
@@ -758,10 +758,10 @@
         <v>894</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>219030</v>
+        <v>198468</v>
       </c>
     </row>
     <row r="17">
@@ -777,10 +777,10 @@
         <v>400</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>445</v>
+        <v>405</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>178000</v>
+        <v>162000</v>
       </c>
     </row>
     <row r="18">
@@ -796,10 +796,10 @@
         <v>400</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>434</v>
+        <v>395</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>173600</v>
+        <v>158000</v>
       </c>
     </row>
     <row r="19">
@@ -815,10 +815,10 @@
         <v>455</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>321</v>
+        <v>292</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>146055</v>
+        <v>132860</v>
       </c>
     </row>
     <row r="20">
@@ -834,10 +834,10 @@
         <v>260</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>321</v>
+        <v>292</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>83460</v>
+        <v>75920</v>
       </c>
     </row>
     <row r="21">
@@ -853,10 +853,10 @@
         <v>344</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>76368</v>
+        <v>69488</v>
       </c>
     </row>
     <row r="22">
@@ -872,10 +872,10 @@
         <v>300</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>66600</v>
+        <v>60600</v>
       </c>
     </row>
     <row r="23">
@@ -884,17 +884,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>60</v>
+        <v>535</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1046</v>
+        <v>107</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>62760</v>
+        <v>57245</v>
       </c>
     </row>
     <row r="24">
@@ -903,17 +903,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
+          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>535</v>
+        <v>60</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>117</v>
+        <v>951</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>62595</v>
+        <v>57060</v>
       </c>
     </row>
     <row r="25">
@@ -929,10 +929,10 @@
         <v>260</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>57720</v>
+        <v>52520</v>
       </c>
     </row>
     <row r="26">
@@ -948,10 +948,10 @@
         <v>200</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>44400</v>
+        <v>40400</v>
       </c>
     </row>
     <row r="27">
@@ -967,10 +967,10 @@
         <v>325</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>42575</v>
+        <v>38675</v>
       </c>
     </row>
     <row r="28">
@@ -986,10 +986,10 @@
         <v>25</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1279</v>
+        <v>1163</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>31975</v>
+        <v>29075</v>
       </c>
     </row>
     <row r="29">
@@ -1005,10 +1005,10 @@
         <v>31</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1023</v>
+        <v>930</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>31713</v>
+        <v>28830</v>
       </c>
     </row>
     <row r="30">
@@ -1024,10 +1024,10 @@
         <v>35</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>895</v>
+        <v>814</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>31325</v>
+        <v>28490</v>
       </c>
     </row>
     <row r="31">
@@ -1043,10 +1043,10 @@
         <v>30</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>445</v>
+        <v>405</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>13350</v>
+        <v>12150</v>
       </c>
     </row>
     <row r="32">
@@ -1062,10 +1062,10 @@
         <v>60</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>11700</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="33">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="5" t="n">
-        <v>23468212</v>
+        <v>21330586</v>
       </c>
     </row>
   </sheetData>
@@ -1195,13 +1195,13 @@
         <v>12</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>620</v>
+        <v>563</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>5625260</v>
+        <v>5108099</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>513550</v>
+        <v>461090</v>
       </c>
     </row>
     <row r="3">
@@ -1232,13 +1232,13 @@
         <v>14.9</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>560</v>
+        <v>510</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3990560</v>
+        <v>3634260</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>359799</v>
+        <v>333568</v>
       </c>
     </row>
     <row r="4">
@@ -1269,13 +1269,13 @@
         <v>15.6</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>803</v>
+        <v>730</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3629560</v>
+        <v>3299600</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>328848</v>
+        <v>298953</v>
       </c>
     </row>
     <row r="5">
@@ -1306,13 +1306,13 @@
         <v>12</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>437</v>
+        <v>397</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1876478</v>
+        <v>1704718</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>171189</v>
+        <v>154455</v>
       </c>
     </row>
     <row r="6">
@@ -1343,13 +1343,13 @@
         <v>12</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>1616</v>
+        <v>1470</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1582064</v>
+        <v>1439130</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>143379</v>
+        <v>131235</v>
       </c>
     </row>
     <row r="7">
@@ -1380,13 +1380,13 @@
         <v>12</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>821485</v>
+        <v>744366</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>75453</v>
+        <v>66155</v>
       </c>
     </row>
     <row r="8">
@@ -1417,13 +1417,13 @@
         <v>12</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>812640</v>
+        <v>738148</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>73828</v>
+        <v>66501</v>
       </c>
     </row>
     <row r="9">
@@ -1454,13 +1454,13 @@
         <v>12</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>673</v>
+        <v>612</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>753760</v>
+        <v>685440</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>68546</v>
+        <v>62518</v>
       </c>
     </row>
     <row r="10">
@@ -1491,13 +1491,13 @@
         <v>3.8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>715650</v>
+        <v>649590</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>64482</v>
+        <v>57619</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>12</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1206</v>
+        <v>1096</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>631944</v>
+        <v>574304</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>57417</v>
+        <v>52007</v>
       </c>
     </row>
     <row r="12">
@@ -1565,13 +1565,13 @@
         <v>36</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>587</v>
+        <v>533</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>567042</v>
+        <v>514878</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>51755</v>
+        <v>46436</v>
       </c>
     </row>
     <row r="13">
@@ -1600,13 +1600,13 @@
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" s="3" t="n">
-        <v>1179</v>
+        <v>1071</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>468063</v>
+        <v>425187</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>42700</v>
+        <v>38493</v>
       </c>
     </row>
     <row r="14">
@@ -1637,13 +1637,13 @@
         <v>12</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1089</v>
+        <v>990</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>364815</v>
+        <v>331650</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>33246</v>
+        <v>30224</v>
       </c>
     </row>
     <row r="15">
@@ -1674,13 +1674,13 @@
         <v>12</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>857</v>
+        <v>779</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>295665</v>
+        <v>268755</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>27025</v>
+        <v>24536</v>
       </c>
     </row>
     <row r="16">
@@ -1711,13 +1711,13 @@
         <v>12</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>219030</v>
+        <v>198468</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>20118</v>
+        <v>17639</v>
       </c>
     </row>
     <row r="17">
@@ -1746,13 +1746,13 @@
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" s="3" t="n">
-        <v>445</v>
+        <v>405</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>178000</v>
+        <v>162000</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>16115</v>
+        <v>14832</v>
       </c>
     </row>
     <row r="18">
@@ -1781,13 +1781,13 @@
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" s="3" t="n">
-        <v>434</v>
+        <v>395</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>173600</v>
+        <v>158000</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>15671</v>
+        <v>14428</v>
       </c>
     </row>
     <row r="19">
@@ -1818,13 +1818,13 @@
         <v>12</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>321</v>
+        <v>292</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>146055</v>
+        <v>132860</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>13242</v>
+        <v>12121</v>
       </c>
     </row>
     <row r="20">
@@ -1855,13 +1855,13 @@
         <v>12</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>321</v>
+        <v>292</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>83460</v>
+        <v>75920</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>7567</v>
+        <v>6926</v>
       </c>
     </row>
     <row r="21">
@@ -1890,13 +1890,13 @@
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" s="3" t="n">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>76368</v>
+        <v>69488</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>6788</v>
+        <v>6233</v>
       </c>
     </row>
     <row r="22">
@@ -1927,13 +1927,13 @@
         <v>0</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>66600</v>
+        <v>60600</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>6131</v>
+        <v>5628</v>
       </c>
     </row>
     <row r="23">
@@ -1942,35 +1942,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>60</v>
+        <v>535</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>30</v>
+        <v>465</v>
       </c>
       <c r="H23" t="n">
         <v>12</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1046</v>
+        <v>107</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>62760</v>
+        <v>57245</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>5729</v>
+        <v>5382</v>
       </c>
     </row>
     <row r="24">
@@ -1979,35 +1979,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
+          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>535</v>
+        <v>60</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>465</v>
+        <v>30</v>
       </c>
       <c r="H24" t="n">
         <v>12</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>117</v>
+        <v>951</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>62595</v>
+        <v>57060</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>5546</v>
+        <v>5213</v>
       </c>
     </row>
     <row r="25">
@@ -2036,13 +2036,13 @@
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" s="3" t="n">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>57720</v>
+        <v>52520</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>5313</v>
+        <v>4878</v>
       </c>
     </row>
     <row r="26">
@@ -2071,13 +2071,13 @@
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" s="3" t="n">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>44400</v>
+        <v>40400</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>4087</v>
+        <v>3752</v>
       </c>
     </row>
     <row r="27">
@@ -2108,13 +2108,13 @@
         <v>12</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>42575</v>
+        <v>38675</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>3911</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="28">
@@ -2145,13 +2145,13 @@
         <v>12</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1279</v>
+        <v>1163</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>31975</v>
+        <v>29075</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>2902</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="29">
@@ -2180,13 +2180,13 @@
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" s="3" t="n">
-        <v>1023</v>
+        <v>930</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>31713</v>
+        <v>28830</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>2882</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="30">
@@ -2217,13 +2217,13 @@
         <v>12</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>895</v>
+        <v>814</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>31325</v>
+        <v>28490</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2838</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="31">
@@ -2252,13 +2252,13 @@
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" s="3" t="n">
-        <v>445</v>
+        <v>405</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>13350</v>
+        <v>12150</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1210</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="32">
@@ -2289,13 +2289,13 @@
         <v>12</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>11700</v>
+        <v>10680</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1043</v>
+        <v>992</v>
       </c>
     </row>
     <row r="33">
@@ -2323,10 +2323,10 @@
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="6" t="inlineStr"/>
       <c r="J33" s="5" t="n">
-        <v>23468212</v>
+        <v>21330586</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>2132310</v>
+        <v>1934311</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Что можно продать оптом.xlsx
+++ b/outputs/Что можно продать оптом.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЧТО МОЖЕМ ОТГРУЗИТЬ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЧТО ОСТАНЕТСЯ У НАС" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЧТО ТЕРЯЕМ НА ХОДОВОМ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2332,4 +2333,1046 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="74" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Просит, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи в месяц, шт</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Прибыль оптом, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Прибыль на WB, руб</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Потеряем, руб</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Во сколько раз WB выгоднее</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>563</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>140960</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1184800</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1043840</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>40599</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>462465</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>421866</v>
+      </c>
+      <c r="H3" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>64746</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>455940</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>391194</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1369</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>46810</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>197800</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>150990</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>19551</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>170070</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>150519</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>21475</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>131600</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>110125</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>13460</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>121492</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>108032</v>
+      </c>
+      <c r="H8" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>5628</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>105510</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>99882</v>
+      </c>
+      <c r="H9" t="n">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>31424</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>128080</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>96656</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>325</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>15712</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>109720</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>94008</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>31008</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>122400</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>91392</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>709</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>31400</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>104200</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>72800</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>342</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>31740</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>98940</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>67200</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/Подтягивающий бустер-крем с ретинолом для лица</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>30492</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>91980</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>61488</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>62752</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>55952</v>
+      </c>
+      <c r="H16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной крем с экстрактом ласточкиного гнезда</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>11838</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>60840</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>49002</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen Water Full Moist Cream [100g] / Увлажняющий крем с коллагеном</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>9716</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>54300</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>44584</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>15816</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>56240</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>40424</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>15504</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>55290</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>39786</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]/ Шампунь с черным чесноком против выпадения волос</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>3569</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>34272</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>30703</v>
+      </c>
+      <c r="H21" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>274</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>11838</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>41280</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>29442</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>269</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>12464</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>38400</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>25936</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>16096</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>41040</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>24944</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>4959</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>26100</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>21141</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>22940</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>20770</v>
+      </c>
+      <c r="H26" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>7992</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>26670</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>18678</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка роллер для глаз</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>3630</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>20093</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>16463</v>
+      </c>
+      <c r="H28" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>5819</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>16753</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>10934</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>10800</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>8788</v>
+      </c>
+      <c r="H30" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозрастной с муцином улитки</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>13530</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>8088</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сыворотка с экстрактом нони для лица</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>4342</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>10311</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>5969</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>1666</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>7047</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>5381</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>26810</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>29240</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>2430</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml] / Тонер для лица увлажняющий с экстрактом алоэ</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>2664</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>4550</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>1886</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr"/>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>18541</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>5375</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>696152</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>4117445</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>3421293</v>
+      </c>
+      <c r="H36" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/Что можно продать оптом.xlsx
+++ b/outputs/Что можно продать оптом.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЧТО МОЖЕМ ОТГРУЗИТЬ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЧТО ОСТАНЕТСЯ У НАС" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЧТО ТЕРЯЕМ НА ХОДОВОМ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЦЕНЫ В КИРГИЗИИ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЧТО ТЕРЯЕМ НА ХОДОВОМ" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2341,6 +2342,1060 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Наша себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Цена в Киргизии, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доставка, руб</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Итого из Киргизии, руб</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Разница, руб</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Разница, %</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Замечание</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1093</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>860</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1030</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>-63</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>686</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>856</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>-44</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица увлажняющая с центеллой</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>820</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>639</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>809</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>770</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>652</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>822</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>853</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>744</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>914</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>864</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>794</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>964</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I7" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сыворотка с экстрактом нони для лица</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>764</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>733</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>903</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="I8" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>740</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>722</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>892</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="I9" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>512</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>620</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="I10" t="n">
+        <v>21</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]/Крем для выравнивания тона и рельефа кожи лица</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>623</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>596</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>766</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="I11" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>720</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>722</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>892</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="I12" t="n">
+        <v>24</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>711</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>881</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="I13" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>397</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>331</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="I14" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]/Сыворотка для выравнивания тона и рельефа кожи лица</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>688</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>706</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>876</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="I15" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>431</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>403</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>573</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="I16" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>664</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>732</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Korea Global</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>902</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="I17" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>639</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="I18" t="n">
+        <v>38</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>647</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>723</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>893</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>246</v>
+      </c>
+      <c r="I19" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>314</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>458</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="I20" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>348</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>338</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>508</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="I21" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>361</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>365</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Korea Global</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>535</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="I22" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>532</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>662</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>832</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="I23" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/Подтягивающий бустер-крем с ретинолом для лица</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>512</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>639</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>809</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="I24" t="n">
+        <v>58</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>556</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>730</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>344</v>
+      </c>
+      <c r="I25" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>485</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>792</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>307</v>
+      </c>
+      <c r="I26" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>322</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="I27" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>368</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>657</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>827</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>459</v>
+      </c>
+      <c r="I28" t="n">
+        <v>124.8</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>711</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>881</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>784</v>
+      </c>
+      <c r="I29" t="n">
+        <v>808.8</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>сверить фасовку</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr"/>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>позиций: 28</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="4" t="inlineStr"/>
+      <c r="J30" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/outputs/Что можно продать оптом.xlsx
+++ b/outputs/Что можно продать оптом.xlsx
@@ -2342,19 +2342,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2385,25 +2386,30 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Вес, кг</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Доставка, руб</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Итого из Киргизии, руб</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Разница, руб</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Разница, %</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Замечание</t>
         </is>
@@ -2415,33 +2421,36 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
+          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1093</v>
+        <v>900</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>860</v>
+        <v>686</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Aibeauty</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>170</v>
+      <c r="F2" s="3" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1030</v>
+        <v>12</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>-63</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-5.8</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>698</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>-202</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-22.4</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2449,33 +2458,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
+          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица увлажняющая с центеллой</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>900</v>
+        <v>820</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>686</v>
+        <v>639</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aibeauty</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>170</v>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0.042</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>856</v>
+        <v>7</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>-44</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
+        <v>646</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>-174</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-21.2</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2483,33 +2495,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица увлажняющая с центеллой</t>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>820</v>
+        <v>1093</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>639</v>
+        <v>860</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Korshop</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>170</v>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.112</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>809</v>
+        <v>19</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>-11</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
+        <v>879</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-19.6</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2531,19 +2546,22 @@
           <t>Korshop</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
-        <v>170</v>
+      <c r="F5" s="3" t="n">
+        <v>0.056</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>822</v>
+        <v>10</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="I5" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
+        <v>662</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>-108</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2565,19 +2583,22 @@
           <t>Aibeauty</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>170</v>
+      <c r="F6" s="3" t="n">
+        <v>0.28</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>914</v>
+        <v>48</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="I6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
+        <v>792</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>-61</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2599,19 +2620,22 @@
           <t>Aibeauty</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
-        <v>170</v>
+      <c r="F7" s="3" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>964</v>
+        <v>12</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I7" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
+        <v>806</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>-58</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2619,33 +2643,36 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сыворотка с экстрактом нони для лица</t>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>764</v>
+        <v>512</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>733</v>
+        <v>450</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Korshop</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>170</v>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.21</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>903</v>
+        <v>36</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>139</v>
-      </c>
-      <c r="I8" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
+        <v>486</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>-26</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2653,33 +2680,36 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
+          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>740</v>
+        <v>314</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>722</v>
+        <v>288</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aibeauty</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>170</v>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>892</v>
+        <v>12</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>152</v>
-      </c>
-      <c r="I9" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
+        <v>300</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>-14</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2687,33 +2717,36 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>512</v>
+        <v>431</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>450</v>
+        <v>403</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aibeauty</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>170</v>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>620</v>
+        <v>12</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>108</v>
-      </c>
-      <c r="I10" t="n">
-        <v>21</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
+        <v>415</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2735,19 +2768,22 @@
           <t>Korshop</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
-        <v>170</v>
+      <c r="F11" s="3" t="n">
+        <v>0.049</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>766</v>
+        <v>8</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>143</v>
-      </c>
-      <c r="I11" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
+        <v>604</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>-19</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2755,33 +2791,36 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
+          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сыворотка с экстрактом нони для лица</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>720</v>
+        <v>764</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>722</v>
+        <v>733</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aibeauty</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>170</v>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0.042</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>892</v>
+        <v>7</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>172</v>
-      </c>
-      <c r="I12" t="n">
-        <v>24</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
+        <v>740</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>-24</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2789,33 +2828,36 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]/Сыворотка для выравнивания тона и рельефа кожи лица</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>708</v>
+        <v>688</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Korshop</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>170</v>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0.042</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>881</v>
+        <v>7</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>173</v>
-      </c>
-      <c r="I13" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
+        <v>713</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2823,33 +2865,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
+          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>397</v>
+        <v>720</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>331</v>
+        <v>722</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Korshop</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>170</v>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0.21</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>501</v>
+        <v>36</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>104</v>
-      </c>
-      <c r="I14" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
+        <v>758</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2857,33 +2902,36 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]/Сыворотка для выравнивания тона и рельефа кожи лица</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>688</v>
+        <v>708</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aibeauty</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>170</v>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.238</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>876</v>
+        <v>40</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>188</v>
-      </c>
-      <c r="I15" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
+        <v>751</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2891,33 +2939,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>431</v>
+        <v>463</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>403</v>
+        <v>469</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Korshop</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>170</v>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0.21</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>573</v>
+        <v>36</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>142</v>
-      </c>
-      <c r="I16" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
+        <v>505</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="J16" t="n">
+        <v>9</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2925,33 +2976,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>664</v>
+        <v>740</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>732</v>
+        <v>722</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Korea Global</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>170</v>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0.5600000000000001</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>902</v>
+        <v>95</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>238</v>
-      </c>
-      <c r="I17" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
+        <v>817</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="J17" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2959,33 +3013,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
+          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>463</v>
+        <v>647</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>469</v>
+        <v>723</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>Aibeauty</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n">
-        <v>170</v>
+      <c r="F18" s="3" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>639</v>
+        <v>12</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>176</v>
-      </c>
-      <c r="I18" t="n">
-        <v>38</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
+        <v>735</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="J18" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2993,33 +3050,36 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
+          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>647</v>
+        <v>348</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>723</v>
+        <v>338</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>Aibeauty</t>
         </is>
       </c>
-      <c r="F19" s="2" t="n">
-        <v>170</v>
+      <c r="F19" s="3" t="n">
+        <v>0.35</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>893</v>
+        <v>59</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>246</v>
-      </c>
-      <c r="I19" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
+        <v>397</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="J19" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3027,33 +3087,36 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>314</v>
+        <v>361</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>288</v>
+        <v>365</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Korshop</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>170</v>
+          <t>Korea Global</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0.28</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>458</v>
+        <v>48</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>144</v>
-      </c>
-      <c r="I20" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
+        <v>413</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="J20" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3061,33 +3124,36 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>348</v>
+        <v>397</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aibeauty</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>170</v>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0.742</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>508</v>
+        <v>126</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>160</v>
-      </c>
-      <c r="I21" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
+        <v>457</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J21" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3095,33 +3161,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
+          <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>361</v>
+        <v>664</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>365</v>
+        <v>732</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>Korea Global</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n">
-        <v>170</v>
+      <c r="F22" s="3" t="n">
+        <v>0.21</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>535</v>
+        <v>36</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>174</v>
-      </c>
-      <c r="I22" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
+        <v>768</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="J22" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3129,33 +3198,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>532</v>
+        <v>161</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>662</v>
+        <v>152</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aibeauty</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>170</v>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0.252</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>832</v>
+        <v>43</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="I23" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
+        <v>195</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="J23" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3177,19 +3249,22 @@
           <t>Aibeauty</t>
         </is>
       </c>
-      <c r="F24" s="2" t="n">
-        <v>170</v>
+      <c r="F24" s="3" t="n">
+        <v>0.021</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>809</v>
+        <v>4</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>297</v>
-      </c>
-      <c r="I24" t="n">
-        <v>58</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
+        <v>643</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="J24" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3197,33 +3272,36 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
+          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>556</v>
+        <v>532</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>730</v>
+        <v>662</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Korshop</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>170</v>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>0.042</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>900</v>
+        <v>7</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>344</v>
-      </c>
-      <c r="I25" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
+        <v>669</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="J25" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3231,33 +3309,36 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>485</v>
+        <v>556</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>622</v>
+        <v>730</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aibeauty</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>170</v>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>0.14</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>792</v>
+        <v>24</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>307</v>
-      </c>
-      <c r="I26" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="J26" t="inlineStr"/>
+        <v>754</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="J26" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3265,33 +3346,36 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
+          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>161</v>
+        <v>485</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>152</v>
+        <v>622</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Korshop</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>170</v>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0.28</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>322</v>
+        <v>48</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>161</v>
-      </c>
-      <c r="I27" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="J27" t="inlineStr"/>
+        <v>670</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="J27" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3313,19 +3397,22 @@
           <t>Korshop</t>
         </is>
       </c>
-      <c r="F28" s="2" t="n">
-        <v>170</v>
+      <c r="F28" s="3" t="n">
+        <v>0.042</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>827</v>
+        <v>7</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>459</v>
-      </c>
-      <c r="I28" t="n">
-        <v>124.8</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
+        <v>664</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="J28" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3347,19 +3434,22 @@
           <t>Korshop</t>
         </is>
       </c>
-      <c r="F29" s="2" t="n">
-        <v>170</v>
+      <c r="F29" s="3" t="n">
+        <v>0.042</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>881</v>
+        <v>7</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>784</v>
-      </c>
-      <c r="I29" t="n">
-        <v>808.8</v>
-      </c>
-      <c r="J29" t="inlineStr">
+        <v>718</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>621</v>
+      </c>
+      <c r="J29" t="n">
+        <v>640.7</v>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>сверить фасовку</t>
         </is>
@@ -3379,11 +3469,12 @@
           <t>позиций: 28</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr"/>
+      <c r="F30" s="6" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="4" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="4" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/Что можно продать оптом.xlsx
+++ b/outputs/Что можно продать оптом.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЧТО МОЖЕМ ОТГРУЗИТЬ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЧТО ОСТАНЕТСЯ У НАС" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЦЕНЫ В КИРГИЗИИ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЧТО ТЕРЯЕМ НА ХОДОВОМ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО БРЕНДАМ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЧТО МОЖЕМ ОТГРУЗИТЬ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЧТО ОСТАНЕТСЯ У НАС" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЦЕНЫ В КИРГИЗИИ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЧТО ТЕРЯЕМ НА ХОДОВОМ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,7 +40,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -56,6 +57,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -69,15 +75,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -444,7 +453,417 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Бренд</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Позиций</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Отдаем, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Сумма, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Прибыль, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Останется у нас, шт</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Теряем на ходовом, руб</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>15653</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>9476199</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>857692</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>2325</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>148826</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DEOPROCE</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>320000</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>29260</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>30703</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>4774</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>872598</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>78110</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3670</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>172682</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ETUDE</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>4294</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1704718</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>154455</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>2985</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>391194</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1753</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>748828</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>67493</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1518121</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>4962</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>1151614</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>102841</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>5715</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>107096</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LEBELAGE</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>325</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>38675</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>3526</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>20770</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>894</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>934444</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>84824</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1725</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>628337</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>8092</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>4149138</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>380004</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>298808</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>12150</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1113</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SOME BY MI</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>29075</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>2645</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>10934</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>THE ORDINARY</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>28830</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>2620</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>1376</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1864317</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>169728</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>ВСЕГО</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>43009</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>21330586</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>1934311</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>18595</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>3421293</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -482,606 +901,749 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/Подтягивающий бустер-крем с ретинолом для лица</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>9073</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>563</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>5108099</v>
-      </c>
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="6" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
+          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>7126</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>510</v>
+        <v>60</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>951</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3634260</v>
+        <v>57060</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4520</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>730</v>
+        <v>345</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>779</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3299600</v>
+        <v>268755</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4294</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>397</v>
+        <v>535</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>107</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1704718</v>
+        <v>57245</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>979</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>1470</v>
+        <v>1120</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>612</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1439130</v>
+        <v>685440</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
+          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/Подтягивающий бустер-крем с ретинолом для лица</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>3353</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>222</v>
+        <v>9073</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>563</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>744366</v>
+        <v>5108099</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
+          <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1693</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>436</v>
+        <v>4520</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>730</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>738148</v>
+        <v>3299600</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>1120</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>612</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>685440</v>
-      </c>
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>DEOPROCE</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
+          <t>DEOPROCE RINSE - BLACK GARLIC INTENSME ENERGY [1000ml] / Бальзам от выпадения волос Чёрный чеснок</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3670</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>177</v>
+        <v>400</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>395</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>649590</v>
+        <v>158000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и пробиотиками</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [1000ml]/ Шампунь с черным чесноком против выпадения волос</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>524</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>1096</v>
+        <v>400</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>405</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>574304</v>
+        <v>162000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>966</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>533</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>514878</v>
-      </c>
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>397</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>1071</v>
+        <v>3670</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>177</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>425187</v>
+        <v>649590</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
+          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>335</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>990</v>
+        <v>344</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>202</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>331650</v>
+        <v>69488</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
+          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>345</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>779</v>
+        <v>200</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>202</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>268755</v>
+        <v>40400</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной крем с экстрактом ласточкиного гнезда</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>894</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>222</v>
+        <v>300</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>202</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>198468</v>
+        <v>60600</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [1000ml]/ Шампунь с черным чесноком против выпадения волос</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>405</v>
+        <v>260</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>202</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>162000</v>
+        <v>52520</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>DEOPROCE RINSE - BLACK GARLIC INTENSME ENERGY [1000ml] / Бальзам от выпадения волос Чёрный чеснок</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>395</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>158000</v>
-      </c>
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>ETUDE</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>455</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>292</v>
+        <v>4294</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>397</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>132860</v>
+        <v>1704718</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>260</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>292</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>75920</v>
-      </c>
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>344</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>202</v>
+        <v>60</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>178</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>69488</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
+          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>202</v>
+        <v>1693</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>436</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>60600</v>
+        <v>738148</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>535</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>107</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>57245</v>
-      </c>
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
+          <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной крем с экстрактом ласточкиного гнезда</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>951</v>
+        <v>894</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>222</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>57060</v>
+        <v>198468</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
+          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="D25" s="3" t="n">
-        <v>202</v>
+      <c r="D25" s="8" t="n">
+        <v>292</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>52520</v>
+        <v>75920</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
+          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>202</v>
+        <v>3353</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>222</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>40400</v>
+        <v>744366</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>325</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>119</v>
+        <v>455</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>292</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>38675</v>
+        <v>132860</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>1163</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>29075</v>
-      </c>
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>LEBELAGE</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>930</v>
+        <v>325</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>119</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>28830</v>
+        <v>38675</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>814</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>28490</v>
-      </c>
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
+          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>405</v>
+        <v>335</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>990</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>12150</v>
+        <v>331650</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
+        <v>23</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>814</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>28490</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>24</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и пробиотиками</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>524</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>1096</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>574304</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>25</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>7126</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>510</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>3634260</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>26</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>966</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>533</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>514878</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>27</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>405</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>12150</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>SOME BY MI</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>28</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>1163</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>29075</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>THE ORDINARY</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="7" t="n"/>
+      <c r="E41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>29</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>178</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>10680</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr"/>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="D42" s="8" t="n">
+        <v>930</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>28830</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>30</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>979</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>1470</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>1439130</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>31</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>397</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>1071</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>425187</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr"/>
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C46" s="4" t="n">
         <v>43009</v>
       </c>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="5" t="n">
+      <c r="D46" s="9" t="inlineStr"/>
+      <c r="E46" s="4" t="n">
         <v>21330586</v>
       </c>
     </row>
@@ -1090,13 +1652,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1170,569 +1732,503 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/Подтягивающий бустер-крем с ретинолом для лица</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>9493</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>9073</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>420</v>
-      </c>
-      <c r="H2" t="n">
-        <v>12</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>563</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>5108099</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>461090</v>
-      </c>
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="n"/>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="7" t="n"/>
+      <c r="J2" s="6" t="n"/>
+      <c r="K2" s="6" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>7126</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>25020</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>1369</v>
-      </c>
       <c r="F3" s="2" t="n">
-        <v>7126</v>
+        <v>60</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>510</v>
+        <v>12</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>951</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3634260</v>
+        <v>57060</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>333568</v>
+        <v>5213</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4520</v>
+        <v>1500</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>40008</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2027</v>
+        <v>77</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>4520</v>
+        <v>345</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0</v>
+        <v>1155</v>
       </c>
       <c r="H4" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>730</v>
+        <v>12</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>779</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3299600</v>
+        <v>268755</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>298953</v>
+        <v>24536</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>7279</v>
+        <v>1000</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>199</v>
+        <v>31</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>4294</v>
+        <v>535</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2985</v>
+        <v>465</v>
       </c>
       <c r="H5" t="n">
         <v>12</v>
       </c>
-      <c r="I5" s="3" t="n">
-        <v>397</v>
+      <c r="I5" s="8" t="n">
+        <v>107</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1704718</v>
+        <v>57245</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>154455</v>
+        <v>5382</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1009</v>
+        <v>1375</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>979</v>
+        <v>1120</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="H6" t="n">
         <v>12</v>
       </c>
-      <c r="I6" s="3" t="n">
-        <v>1470</v>
+      <c r="I6" s="8" t="n">
+        <v>612</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1439130</v>
+        <v>685440</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>131235</v>
+        <v>62518</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
+          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/Подтягивающий бустер-крем с ретинолом для лица</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>7463</v>
+        <v>9493</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>274</v>
+        <v>28</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>3353</v>
+        <v>9073</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>4110</v>
+        <v>420</v>
       </c>
       <c r="H7" t="n">
         <v>12</v>
       </c>
-      <c r="I7" s="3" t="n">
-        <v>222</v>
+      <c r="I7" s="8" t="n">
+        <v>563</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>744366</v>
+        <v>5108099</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>66155</v>
+        <v>461090</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
+          <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>3493</v>
+        <v>4520</v>
       </c>
       <c r="D8" s="2" t="n">
+        <v>40008</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>2027</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>4520</v>
+      </c>
+      <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>1693</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>1800</v>
-      </c>
       <c r="H8" t="n">
-        <v>12</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>436</v>
+        <v>15.6</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>730</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>738148</v>
+        <v>3299600</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>66501</v>
+        <v>298953</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>1375</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>1120</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>255</v>
-      </c>
-      <c r="H9" t="n">
-        <v>12</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>612</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>685440</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>62518</v>
-      </c>
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>DEOPROCE</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
+          <t>DEOPROCE RINSE - BLACK GARLIC INTENSME ENERGY [1000ml] / Бальзам от выпадения волос Чёрный чеснок</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>7340</v>
+        <v>400</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>709</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>3670</v>
+        <v>400</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>3670</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>177</v>
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" s="8" t="n">
+        <v>395</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>649590</v>
+        <v>158000</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>57619</v>
+        <v>14428</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и пробиотиками</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [1000ml]/ Шампунь с черным чесноком против выпадения волос</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>614</v>
+        <v>400</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>524</v>
+        <v>400</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="H11" t="n">
-        <v>12</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>1096</v>
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" s="8" t="n">
+        <v>405</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>574304</v>
+        <v>162000</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>52007</v>
+        <v>14832</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>966</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>360</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>966</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>36</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>533</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>514878</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>46436</v>
-      </c>
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>397</v>
+        <v>7340</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>397</v>
+        <v>3670</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" s="3" t="n">
-        <v>1071</v>
+        <v>3670</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>177</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>425187</v>
+        <v>649590</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>38493</v>
+        <v>57619</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
+          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1355</v>
+        <v>344</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1020</v>
-      </c>
-      <c r="H14" t="n">
-        <v>12</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>990</v>
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" s="8" t="n">
+        <v>202</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>331650</v>
+        <v>69488</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>30224</v>
+        <v>6233</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
+          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1500</v>
+        <v>200</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>345</v>
+        <v>200</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>1155</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>779</v>
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" s="8" t="n">
+        <v>202</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>268755</v>
+        <v>40400</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>24536</v>
+        <v>3752</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной крем с экстрактом ласточкиного гнезда</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1614</v>
+        <v>300</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>894</v>
+        <v>300</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>12</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>222</v>
+        <v>0</v>
+      </c>
+      <c r="I16" s="8" t="n">
+        <v>202</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>198468</v>
+        <v>60600</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>17639</v>
+        <v>5628</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [1000ml]/ Шампунь с черным чесноком против выпадения волос</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>400</v>
+        <v>260</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0</v>
@@ -1741,593 +2237,880 @@
         <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>400</v>
+        <v>260</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" s="3" t="n">
-        <v>405</v>
+      <c r="I17" s="8" t="n">
+        <v>202</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>162000</v>
+        <v>52520</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>14832</v>
+        <v>4878</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>DEOPROCE RINSE - BLACK GARLIC INTENSME ENERGY [1000ml] / Бальзам от выпадения волос Чёрный чеснок</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" s="3" t="n">
-        <v>395</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>158000</v>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>14428</v>
-      </c>
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>ETUDE</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>800</v>
+        <v>7279</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>23</v>
+        <v>199</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>455</v>
+        <v>4294</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>345</v>
+        <v>2985</v>
       </c>
       <c r="H19" t="n">
         <v>12</v>
       </c>
-      <c r="I19" s="3" t="n">
-        <v>292</v>
+      <c r="I19" s="8" t="n">
+        <v>397</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>132860</v>
+        <v>1704718</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>12121</v>
+        <v>154455</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>800</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>260</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>540</v>
-      </c>
-      <c r="H20" t="n">
-        <v>12</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>292</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>75920</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>6926</v>
-      </c>
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="7" t="n"/>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>344</v>
+        <v>300</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>344</v>
+        <v>60</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" s="3" t="n">
-        <v>202</v>
+        <v>240</v>
+      </c>
+      <c r="H21" t="n">
+        <v>12</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>178</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>69488</v>
+        <v>10680</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>6233</v>
+        <v>992</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
+          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>300</v>
+        <v>3493</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>300</v>
+        <v>1693</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>202</v>
+        <v>12</v>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>436</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>60600</v>
+        <v>738148</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>5628</v>
+        <v>66501</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>535</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>465</v>
-      </c>
-      <c r="H23" t="n">
-        <v>12</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>107</v>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>57245</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>5382</v>
-      </c>
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="7" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
+          <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной крем с экстрактом ласточкиного гнезда</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>90</v>
+        <v>1614</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>60</v>
+        <v>894</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>30</v>
+        <v>720</v>
       </c>
       <c r="H24" t="n">
         <v>12</v>
       </c>
-      <c r="I24" s="3" t="n">
-        <v>951</v>
+      <c r="I24" s="8" t="n">
+        <v>222</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>57060</v>
+        <v>198468</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>5213</v>
+        <v>17639</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
+          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>260</v>
+        <v>800</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>260</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" s="3" t="n">
-        <v>202</v>
+        <v>540</v>
+      </c>
+      <c r="H25" t="n">
+        <v>12</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>292</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>52520</v>
+        <v>75920</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>4878</v>
+        <v>6926</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
+          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>200</v>
+        <v>7463</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>274</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>200</v>
+        <v>3353</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" s="3" t="n">
-        <v>202</v>
+        <v>4110</v>
+      </c>
+      <c r="H26" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>222</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>40400</v>
+        <v>744366</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>3752</v>
+        <v>66155</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>325</v>
+        <v>455</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>75</v>
+        <v>345</v>
       </c>
       <c r="H27" t="n">
         <v>12</v>
       </c>
-      <c r="I27" s="3" t="n">
-        <v>119</v>
+      <c r="I27" s="8" t="n">
+        <v>292</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>38675</v>
+        <v>132860</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>3526</v>
+        <v>12121</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H28" t="n">
-        <v>12</v>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>1163</v>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>29075</v>
-      </c>
-      <c r="K28" s="2" t="n">
-        <v>2645</v>
-      </c>
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>LEBELAGE</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="7" t="n"/>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>31</v>
+        <v>400</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>31</v>
+        <v>325</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" s="3" t="n">
-        <v>930</v>
+        <v>75</v>
+      </c>
+      <c r="H29" t="n">
+        <v>12</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>119</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>28830</v>
+        <v>38675</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>2620</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>650</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>615</v>
-      </c>
-      <c r="H30" t="n">
-        <v>12</v>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>814</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>28490</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>2593</v>
-      </c>
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="7" t="n"/>
+      <c r="J30" s="6" t="n"/>
+      <c r="K30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
+          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>30</v>
+        <v>1355</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>30</v>
+        <v>335</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" s="3" t="n">
-        <v>405</v>
+        <v>1020</v>
+      </c>
+      <c r="H31" t="n">
+        <v>12</v>
+      </c>
+      <c r="I31" s="8" t="n">
+        <v>990</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>12150</v>
+        <v>331650</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1113</v>
+        <v>30224</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>300</v>
+        <v>650</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>240</v>
+        <v>615</v>
       </c>
       <c r="H32" t="n">
         <v>12</v>
       </c>
-      <c r="I32" s="3" t="n">
-        <v>178</v>
+      <c r="I32" s="8" t="n">
+        <v>814</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>10680</v>
+        <v>28490</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>992</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr"/>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="A33" t="n">
+        <v>24</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и пробиотиками</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>614</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>524</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="H33" t="n">
+        <v>12</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>1096</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>574304</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>52007</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="7" t="n"/>
+      <c r="J34" s="6" t="n"/>
+      <c r="K34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>25</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>7126</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>25020</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>1369</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>7126</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>510</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>3634260</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>333568</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>26</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>966</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>966</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>36</v>
+      </c>
+      <c r="I36" s="8" t="n">
+        <v>533</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>514878</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>46436</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="7" t="n"/>
+      <c r="J37" s="6" t="n"/>
+      <c r="K37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>27</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" s="8" t="n">
+        <v>405</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>12150</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>SOME BY MI</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n"/>
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="7" t="n"/>
+      <c r="J39" s="6" t="n"/>
+      <c r="K39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>28</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H40" t="n">
+        <v>12</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>1163</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>29075</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>THE ORDINARY</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="n"/>
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="7" t="n"/>
+      <c r="J41" s="6" t="n"/>
+      <c r="K41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>29</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" s="8" t="n">
+        <v>930</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>28830</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>2620</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="6" t="n"/>
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="7" t="n"/>
+      <c r="J43" s="6" t="n"/>
+      <c r="K43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>30</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>979</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H44" t="n">
+        <v>12</v>
+      </c>
+      <c r="I44" s="8" t="n">
+        <v>1470</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>1439130</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>131235</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>31</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>397</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>397</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" s="8" t="n">
+        <v>1071</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>425187</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>38493</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr"/>
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C46" s="4" t="n">
         <v>61604</v>
       </c>
-      <c r="D33" s="5" t="n">
+      <c r="D46" s="4" t="n">
         <v>66888</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E46" s="4" t="n">
         <v>5108</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="F46" s="4" t="n">
         <v>43009</v>
       </c>
-      <c r="G33" s="5" t="n">
+      <c r="G46" s="4" t="n">
         <v>18595</v>
       </c>
-      <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="5" t="n">
+      <c r="H46" s="3" t="inlineStr"/>
+      <c r="I46" s="9" t="inlineStr"/>
+      <c r="J46" s="4" t="n">
         <v>21330586</v>
       </c>
-      <c r="K33" s="5" t="n">
+      <c r="K46" s="4" t="n">
         <v>1934311</v>
       </c>
     </row>
@@ -2336,13 +3119,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2416,1078 +3199,1197 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>686</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Aibeauty</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>-202</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-22.4</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="6" t="n"/>
+      <c r="I2" s="6" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица увлажняющая с центеллой</t>
+          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>820</v>
+        <v>864</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>639</v>
+        <v>794</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Korshop</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0.042</v>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>646</v>
+        <v>806</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-174</v>
+        <v>-58</v>
       </c>
       <c r="J3" t="n">
-        <v>-21.2</v>
+        <v>-6.7</v>
       </c>
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1093</v>
+        <v>708</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>860</v>
+        <v>711</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aibeauty</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0.112</v>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>0.238</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>879</v>
+        <v>751</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-214</v>
+        <v>43</v>
       </c>
       <c r="J4" t="n">
-        <v>-19.6</v>
+        <v>6.1</v>
       </c>
       <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>770</v>
+        <v>97</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>652</v>
+        <v>711</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Korshop</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>0.056</v>
+      <c r="F5" s="8" t="n">
+        <v>0.042</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>662</v>
+        <v>718</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-108</v>
+        <v>621</v>
       </c>
       <c r="J5" t="n">
-        <v>-14.1</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
+        <v>640.7</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>сверить фасовку</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]/Крем для выравнивания тона и рельефа кожи лица</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>853</v>
+        <v>623</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>744</v>
+        <v>596</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aibeauty</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0.28</v>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>0.049</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>792</v>
+        <v>604</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-61</v>
+        <v>-19</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.2</v>
+        <v>-3.1</v>
       </c>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>864</v>
+        <v>556</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>794</v>
+        <v>730</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aibeauty</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0.07000000000000001</v>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>0.14</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>806</v>
+        <v>754</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-58</v>
+        <v>198</v>
       </c>
       <c r="J7" t="n">
-        <v>-6.7</v>
+        <v>35.6</v>
       </c>
       <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]/Сыворотка для выравнивания тона и рельефа кожи лица</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>688</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>706</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="G8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>512</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>450</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Aibeauty</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>36</v>
-      </c>
       <c r="H8" s="2" t="n">
-        <v>486</v>
+        <v>713</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-26</v>
+        <v>25</v>
       </c>
       <c r="J8" t="n">
-        <v>-5.1</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
+          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сыворотка с экстрактом нони для лица</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>314</v>
+        <v>764</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>288</v>
+        <v>733</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Korshop</t>
         </is>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>0.07000000000000001</v>
+      <c r="F9" s="8" t="n">
+        <v>0.042</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>300</v>
+        <v>740</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-14</v>
+        <v>-24</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.4</v>
+        <v>-3.1</v>
       </c>
       <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
+          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>431</v>
+        <v>720</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>403</v>
+        <v>722</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Korshop</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>0.07000000000000001</v>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>0.21</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>415</v>
+        <v>758</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
+        <v>38</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.7</v>
+        <v>5.3</v>
       </c>
       <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]/Крем для выравнивания тона и рельефа кожи лица</t>
+          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/Подтягивающий бустер-крем с ретинолом для лица</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>623</v>
+        <v>512</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>596</v>
+        <v>639</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Korshop</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>0.049</v>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>0.021</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>604</v>
+        <v>643</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-19</v>
+        <v>131</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.1</v>
+        <v>25.5</v>
       </c>
       <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сыворотка с экстрактом нони для лица</t>
+          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>764</v>
+        <v>532</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>733</v>
+        <v>662</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Korshop</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="n">
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n">
         <v>0.042</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>7</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>740</v>
+        <v>669</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-24</v>
+        <v>137</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.1</v>
+        <v>25.7</v>
       </c>
       <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]/Сыворотка для выравнивания тона и рельефа кожи лица</t>
+          <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>688</v>
+        <v>664</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>706</v>
+        <v>732</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aibeauty</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>0.042</v>
+          <t>Korea Global</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>0.21</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>713</v>
+        <v>768</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7</v>
+        <v>15.7</v>
       </c>
       <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>720</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>722</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Aibeauty</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>758</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>ETUDE</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>708</v>
+        <v>361</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>711</v>
+        <v>365</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Korshop</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0.238</v>
+          <t>Korea Global</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>0.28</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>751</v>
+        <v>413</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="J15" t="n">
-        <v>6.1</v>
+        <v>14.4</v>
       </c>
       <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>463</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>469</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Aibeauty</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>505</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J16" t="n">
-        <v>9</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>740</v>
+        <v>397</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>722</v>
+        <v>331</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aibeauty</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>0.5600000000000001</v>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>0.742</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>817</v>
+        <v>457</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J17" t="n">
-        <v>10.4</v>
+        <v>15.2</v>
       </c>
       <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
+          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>647</v>
+        <v>348</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>723</v>
+        <v>338</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>Aibeauty</t>
         </is>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>0.07000000000000001</v>
+      <c r="F18" s="8" t="n">
+        <v>0.35</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>735</v>
+        <v>397</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="J18" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>348</v>
+        <v>161</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>338</v>
+        <v>152</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aibeauty</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>0.35</v>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>0.252</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>397</v>
+        <v>195</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="J19" t="n">
-        <v>14.2</v>
+        <v>20.8</v>
       </c>
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
+          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>361</v>
+        <v>314</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>365</v>
+        <v>288</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Korea Global</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>0.28</v>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>413</v>
+        <v>300</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>52</v>
+        <v>-14</v>
       </c>
       <c r="J20" t="n">
-        <v>14.4</v>
+        <v>-4.4</v>
       </c>
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>397</v>
+        <v>431</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>331</v>
+        <v>403</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>Korshop</t>
         </is>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>0.742</v>
+      <c r="F21" s="8" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>126</v>
+        <v>12</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>457</v>
+        <v>415</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>60</v>
+        <v>-16</v>
       </c>
       <c r="J21" t="n">
-        <v>15.2</v>
+        <v>-3.7</v>
       </c>
       <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>664</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>732</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Korea Global</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>768</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>104</v>
-      </c>
-      <c r="J22" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>HEIMISH</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
+          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>161</v>
+        <v>770</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>152</v>
+        <v>652</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>Korshop</t>
         </is>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>0.252</v>
+      <c r="F23" s="8" t="n">
+        <v>0.056</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>195</v>
+        <v>662</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>34</v>
+        <v>-108</v>
       </c>
       <c r="J23" t="n">
-        <v>20.8</v>
+        <v>-14.1</v>
       </c>
       <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/Подтягивающий бустер-крем с ретинолом для лица</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>512</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>639</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Aibeauty</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>643</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="J24" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
+          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>532</v>
+        <v>900</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>662</v>
+        <v>686</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>Aibeauty</t>
         </is>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>0.042</v>
+      <c r="F25" s="8" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>669</v>
+        <v>698</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>137</v>
+        <v>-202</v>
       </c>
       <c r="J25" t="n">
-        <v>25.7</v>
+        <v>-22.4</v>
       </c>
       <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
+          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>556</v>
+        <v>647</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Korshop</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>0.14</v>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>754</v>
+        <v>735</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>198</v>
+        <v>88</v>
       </c>
       <c r="J26" t="n">
-        <v>35.6</v>
+        <v>13.6</v>
       </c>
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
+          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>485</v>
+        <v>853</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>622</v>
+        <v>744</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>Aibeauty</t>
         </is>
       </c>
-      <c r="F27" s="3" t="n">
+      <c r="F27" s="8" t="n">
         <v>0.28</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>48</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>670</v>
+        <v>792</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>185</v>
+        <v>-61</v>
       </c>
       <c r="J27" t="n">
-        <v>38.2</v>
+        <v>-7.2</v>
       </c>
       <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
+        <v>22</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>740</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>722</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>817</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="J28" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>23</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="J30" t="n">
+        <v>9</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>24</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>485</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>670</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="J31" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>25</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>1093</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>860</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>879</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-19.6</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>26</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>512</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>486</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>-26</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
         <v>27</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица увлажняющая с центеллой</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>820</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>639</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>646</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>-174</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-21.2</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="6" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>28</v>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
+      <c r="C36" s="2" t="n">
         <v>368</v>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D36" s="2" t="n">
         <v>657</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Korshop</t>
         </is>
       </c>
-      <c r="F28" s="3" t="n">
+      <c r="F36" s="8" t="n">
         <v>0.042</v>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="H28" s="2" t="n">
+      <c r="H36" s="2" t="n">
         <v>664</v>
       </c>
-      <c r="I28" s="2" t="n">
+      <c r="I36" s="2" t="n">
         <v>296</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J36" t="n">
         <v>80.5</v>
       </c>
-      <c r="K28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>711</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Korshop</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>718</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>621</v>
-      </c>
-      <c r="J29" t="n">
-        <v>640.7</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>сверить фасовку</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr"/>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr"/>
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>позиций: 28</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="4" t="inlineStr"/>
-      <c r="K30" s="4" t="inlineStr"/>
+      <c r="F37" s="9" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr"/>
+      <c r="K37" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3543,112 +4445,98 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>4000</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>563</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>140960</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1184800</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1043840</v>
-      </c>
-      <c r="H2" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="n"/>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>40599</v>
+        <v>2012</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>462465</v>
+        <v>10800</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>421866</v>
+        <v>8788</v>
       </c>
       <c r="H3" t="n">
-        <v>11.4</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
+          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сыворотка с экстрактом нони для лица</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1800</v>
+        <v>57</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>199</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>64746</v>
+        <v>4342</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>455940</v>
+        <v>10311</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>391194</v>
+        <v>5969</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
+          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1369</v>
+        <v>5</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>46810</v>
+        <v>1666</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>197800</v>
+        <v>7047</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>150990</v>
+        <v>5381</v>
       </c>
       <c r="H5" t="n">
         <v>4.2</v>
@@ -3656,483 +4544,427 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
+          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/Подтягивающий бустер-крем с ретинолом для лица</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>19551</v>
+        <v>30492</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>170070</v>
+        <v>91980</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>150519</v>
+        <v>61488</v>
       </c>
       <c r="H6" t="n">
-        <v>8.699999999999999</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
+          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>165</v>
+        <v>342</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>21475</v>
+        <v>31740</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>131600</v>
+        <v>98940</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>110125</v>
+        <v>67200</v>
       </c>
       <c r="H7" t="n">
-        <v>6.1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>280</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>13460</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>121492</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>108032</v>
-      </c>
-      <c r="H8" t="n">
-        <v>9</v>
-      </c>
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>DEOPROCE</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]/ Шампунь с черным чесноком против выпадения волос</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>5628</v>
+        <v>3569</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>105510</v>
+        <v>34272</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>99882</v>
+        <v>30703</v>
       </c>
       <c r="H9" t="n">
-        <v>18.7</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>800</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>31424</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>128080</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>96656</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4.1</v>
-      </c>
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>325</v>
+        <v>709</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>15712</v>
+        <v>31400</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>109720</v>
+        <v>104200</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>94008</v>
+        <v>72800</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>31008</v>
+        <v>5628</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>122400</v>
+        <v>105510</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>91392</v>
+        <v>99882</v>
       </c>
       <c r="H12" t="n">
-        <v>3.9</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>709</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>31400</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>104200</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>72800</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3.3</v>
-      </c>
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>ETUDE</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>600</v>
+        <v>1800</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>31740</v>
+        <v>64746</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>98940</v>
+        <v>455940</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>67200</v>
+        <v>391194</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/Подтягивающий бустер-крем с ретинолом для лица</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>600</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>30492</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>91980</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>61488</v>
-      </c>
-      <c r="H15" t="n">
-        <v>3</v>
-      </c>
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
+          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>32</v>
+        <v>182</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>6800</v>
+        <v>16096</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>62752</v>
+        <v>41040</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>55952</v>
+        <v>24944</v>
       </c>
       <c r="H16" t="n">
-        <v>9.199999999999999</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной крем с экстрактом ласточкиного гнезда</t>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>48</v>
+        <v>325</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>11838</v>
+        <v>15712</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>60840</v>
+        <v>109720</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>49002</v>
+        <v>94008</v>
       </c>
       <c r="H17" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Cream [100g] / Увлажняющий крем с коллагеном</t>
+          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>200</v>
+        <v>4000</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>67</v>
+        <v>563</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>9716</v>
+        <v>140960</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>54300</v>
+        <v>1184800</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>44584</v>
+        <v>1043840</v>
       </c>
       <c r="H18" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>15816</v>
+        <v>4959</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>56240</v>
+        <v>26100</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>40424</v>
+        <v>21141</v>
       </c>
       <c r="H19" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
+          <t>FARMSTAY - Collagen Water Full Moist Cream [100g] / Увлажняющий крем с коллагеном</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>15504</v>
+        <v>9716</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>55290</v>
+        <v>54300</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>39786</v>
+        <v>44584</v>
       </c>
       <c r="H20" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]/ Шампунь с черным чесноком против выпадения волос</t>
+          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка роллер для глаз</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>240</v>
+        <v>156</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>3569</v>
+        <v>3630</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>34272</v>
+        <v>20093</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>30703</v>
+        <v>16463</v>
       </c>
       <c r="H21" t="n">
-        <v>9.6</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
+          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>274</v>
+        <v>120</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>11838</v>
+        <v>31424</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>41280</v>
+        <v>128080</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>29442</v>
+        <v>96656</v>
       </c>
       <c r="H22" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -4160,363 +4992,601 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>16096</v>
+        <v>21475</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>41040</v>
+        <v>131600</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>24944</v>
+        <v>110125</v>
       </c>
       <c r="H24" t="n">
-        <v>2.5</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>4959</v>
+        <v>15816</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>26100</v>
+        <v>56240</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>21141</v>
+        <v>40424</v>
       </c>
       <c r="H25" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>2170</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>22940</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>20770</v>
-      </c>
-      <c r="H26" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>HEIMISH</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
+          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>7992</v>
+        <v>31008</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>26670</v>
+        <v>122400</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>18678</v>
+        <v>91392</v>
       </c>
       <c r="H27" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка роллер для глаз</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>156</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>3630</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>20093</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>16463</v>
-      </c>
-      <c r="H28" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
+          <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной крем с экстрактом ласточкиного гнезда</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>5819</v>
+        <v>11838</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>16753</v>
+        <v>60840</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>10934</v>
+        <v>49002</v>
       </c>
       <c r="H29" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
+          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml] / Тонер для лица увлажняющий с экстрактом алоэ</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>2012</v>
+        <v>2664</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>10800</v>
+        <v>4550</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>8788</v>
+        <v>1886</v>
       </c>
       <c r="H30" t="n">
-        <v>5.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозрастной с муцином улитки</t>
+          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>100</v>
+        <v>274</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>5442</v>
+        <v>11838</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>13530</v>
+        <v>41280</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>8088</v>
+        <v>29442</v>
       </c>
       <c r="H31" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сыворотка с экстрактом нони для лица</t>
+          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозрастной с муцином улитки</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>57</v>
+        <v>300</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>4342</v>
+        <v>5442</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>10311</v>
+        <v>13530</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>5969</v>
+        <v>8088</v>
       </c>
       <c r="H32" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D33" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D33" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="E33" s="2" t="n">
-        <v>1666</v>
+        <v>7992</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>7047</v>
+        <v>26670</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>5381</v>
+        <v>18678</v>
       </c>
       <c r="H33" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>26810</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>29240</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>2430</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>LEBELAGE</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
+        <v>26</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>22940</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>20770</v>
+      </c>
+      <c r="H35" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>27</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>40599</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>462465</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>421866</v>
+      </c>
+      <c r="H37" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>28</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>19551</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>170070</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>150519</v>
+      </c>
+      <c r="H38" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>29</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>62752</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>55952</v>
+      </c>
+      <c r="H39" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>30</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>1369</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>46810</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>197800</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>150990</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>31</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>13460</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>121492</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>108032</v>
+      </c>
+      <c r="H42" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>32</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>15504</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>55290</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>39786</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>SOME BY MI</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="6" t="n"/>
+      <c r="H44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>33</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>5819</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>16753</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>10934</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n"/>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="n"/>
+      <c r="H46" s="5" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
         <v>34</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml] / Тонер для лица увлажняющий с экстрактом алоэ</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>2664</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>4550</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>1886</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr"/>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>26810</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>29240</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>2430</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr"/>
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C36" s="5" t="n">
+      <c r="C48" s="4" t="n">
         <v>18541</v>
       </c>
-      <c r="D36" s="5" t="n">
+      <c r="D48" s="4" t="n">
         <v>5375</v>
       </c>
-      <c r="E36" s="5" t="n">
+      <c r="E48" s="4" t="n">
         <v>696152</v>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="F48" s="4" t="n">
         <v>4117445</v>
       </c>
-      <c r="G36" s="5" t="n">
+      <c r="G48" s="4" t="n">
         <v>3421293</v>
       </c>
-      <c r="H36" s="4" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/Что можно продать оптом.xlsx
+++ b/outputs/Что можно продать оптом.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЧТО МОЖЕМ ОТГРУЗИТЬ" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЧТО ОСТАНЕТСЯ У НАС" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЦЕНЫ В КИРГИЗИИ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЧТО ТЕРЯЕМ НА ХОДОВОМ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="НЕ ОТДАВАТЬ, ПРОДАДИМ САМИ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЧТО ТЕРЯЕМ НА ХОДОВОМ" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4389,6 +4390,967 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="68" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Просит, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи в месяц, шт</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Распродадим сами за, мес</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Прибыль оптом, руб</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Прибыль на WB, руб</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Разница, руб</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Во сколько раз WB выгоднее</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="6" t="n"/>
+      <c r="I2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>10800</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>8788</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сыворотка с экстрактом нони для лица</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>4342</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>10311</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>5969</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>1666</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>7047</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>5381</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>342</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>31740</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>98940</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>67200</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>709</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>31400</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>104200</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>72800</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>ETUDE</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>64746</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>455940</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>391194</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>16096</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>41040</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>24944</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>325</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>15712</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>109720</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>94008</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>563</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>140960</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1184800</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>1043840</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen Water Full Moist Cream [100g] / Увлажняющий крем с коллагеном</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>9716</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>54300</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>44584</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка роллер для глаз</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>3630</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>20093</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>16463</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>31424</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>128080</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>96656</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>269</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>12464</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>38400</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>25936</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>21475</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>131600</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>110125</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>15816</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>56240</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>40424</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>HEIMISH</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>31008</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>122400</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>91392</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml] / Тонер для лица увлажняющий с экстрактом алоэ</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>2664</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>4550</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>1886</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>18</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>274</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>11838</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>41280</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>29442</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>19</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозрастной с муцином улитки</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>5442</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>13530</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>8088</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>20</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>40599</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>462465</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>421866</v>
+      </c>
+      <c r="I28" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>21</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>19551</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>170070</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>150519</v>
+      </c>
+      <c r="I29" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>22</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>62752</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>55952</v>
+      </c>
+      <c r="I30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>23</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>1369</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>46810</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>197800</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>150990</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>24</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>15504</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>55290</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>39786</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr"/>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>15466</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>5227</v>
+      </c>
+      <c r="E34" s="9" t="inlineStr"/>
+      <c r="F34" s="4" t="n">
+        <v>583415</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>3581648</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>2998233</v>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/outputs/Что можно продать оптом.xlsx
+++ b/outputs/Что можно продать оптом.xlsx
@@ -10,9 +10,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО БРЕНДАМ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЧТО МОЖЕМ ОТГРУЗИТЬ" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЧТО ОСТАНЕТСЯ У НАС" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЦЕНЫ В КИРГИЗИИ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="НЕ ОТДАВАТЬ, ПРОДАДИМ САМИ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЧТО ТЕРЯЕМ НА ХОДОВОМ" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПРОДАТЬ И ОТКУПИТЬ В КИРГИЗИИ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="НЕ С ЧЕМ СРАВНИТЬ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЦЕНЫ В КИРГИЗИИ" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="НЕ ОТДАВАТЬ, ПРОДАДИМ САМИ" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЧТО ТЕРЯЕМ НА ХОДОВОМ" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3126,7 +3128,3281 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:L40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Просит, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Наша цена, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Цена в Киргизии, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Вес, кг</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Доставка, руб</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Откупим по, руб</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Разница на штуку, руб</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Разница на партию, руб</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Вывод</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="6" t="n"/>
+      <c r="I2" s="6" t="n"/>
+      <c r="J2" s="6" t="n"/>
+      <c r="K2" s="6" t="n"/>
+      <c r="L2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>951</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>794</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>806</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>13050</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>выгодно: откупим дешевле</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>779</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>711</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>751</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>5600</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>выгодно: откупим дешевле</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>711</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>718</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>-611</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>-122200</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>невыгодно: откуп дороже продажи</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]/Крем для выравнивания тона и рельефа кожи лица</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>686</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>596</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>604</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>1066</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>выгодно: откупим дешевле</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>612</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>730</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>754</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>-142</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>-28400</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>невыгодно: откуп дороже продажи</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]/Сыворотка для выравнивания тона и рельефа кожи лица</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>756</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>706</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>713</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>3010</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>выгодно: откупим дешевле</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сыворотка с экстрактом нони для лица</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>840</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>733</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>740</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>5700</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>выгодно: откупим дешевле</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>792</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>722</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>758</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>782</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>выгодно: откупим дешевле</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/Подтягивающий бустер-крем с ретинолом для лица</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>563</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>639</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>643</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>-80</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>-48000</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>невыгодно: откуп дороже продажи</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>585</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>662</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>669</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>-84</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>-50400</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>невыгодно: откуп дороже продажи</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>730</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>732</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Korea Global</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>-38</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>-38000</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>невыгодно: откуп дороже продажи</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>ETUDE</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>397</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>365</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Korea Global</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>413</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>-28800</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>невыгодно: откуп дороже продажи</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>436</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>331</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>457</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>-21</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>-8400</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>невыгодно: откуп дороже продажи</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>383</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>338</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>397</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>-14</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>-56000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>невыгодно: откуп дороже продажи</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>-17</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>-5100</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>невыгодно: откуп дороже продажи</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>345</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>выгодно: откупим дешевле</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>474</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>403</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>29500</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>выгодно: откупим дешевле</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>HEIMISH</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>848</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>652</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>662</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>74400</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>выгодно: откупим дешевле</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="n"/>
+      <c r="L24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>19</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>990</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>686</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>131400</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>выгодно: откупим дешевле</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>20</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>712</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>723</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>735</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>-23</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>-6900</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>невыгодно: откуп дороже продажи</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>21</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>938</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>744</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>792</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>11680</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>выгодно: откупим дешевле</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>22</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>814</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>722</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>817</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>-1050</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>невыгодно: откуп дороже продажи</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="6" t="n"/>
+      <c r="L29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>23</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>510</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>выгодно: откупим дешевле</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>24</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>533</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>670</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>-137</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>-38360</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>невыгодно: откуп дороже продажи</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>25</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>1202</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>860</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>879</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>323</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>83657</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>выгодно: откупим дешевле</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>26</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>564</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Aibeauty</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>486</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>23400</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>выгодно: откупим дешевле</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>27</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица увлажняющая с центеллой</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>902</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>639</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>646</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>8192</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>выгодно: откупим дешевле</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="6" t="n"/>
+      <c r="J35" s="6" t="n"/>
+      <c r="K35" s="6" t="n"/>
+      <c r="L35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>28</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>405</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>657</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>664</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>-259</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>-7770</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>невыгодно: откуп дороже продажи</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6" t="n"/>
+      <c r="J37" s="6" t="n"/>
+      <c r="K37" s="6" t="n"/>
+      <c r="L37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>29</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>1470</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>1423</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Korea Global</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>1457</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>2600</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>выгодно: откупим дешевле</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>30</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>1071</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>1183</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>1217</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>-146</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>-14600</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>невыгодно: откуп дороже продажи</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr"/>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>14234</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="9" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr"/>
+      <c r="J40" s="4" t="inlineStr"/>
+      <c r="K40" s="4" t="n">
+        <v>-36943</v>
+      </c>
+      <c r="L40" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="74" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Наша себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Почему</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>DEOPROCE</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DEOPROCE RINSE - BLACK GARLIC INTENSME ENERGY [1000ml] / Бальзам от выпадения волос Чёрный чеснок</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>359</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>бренд DEOPROCE есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [1000ml]/ Шампунь с черным чесноком против выпадения волос</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>368</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>бренд DEOPROCE есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]/ Шампунь с черным чесноком против выпадения волос</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>151</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>бренд DEOPROCE есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>ELIZAVECCA</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ELIZAVECCA - CER-100 Collagen Ceramide Coating Protein Treatment [100ml] / Коллагеновая маска для волос</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>242</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>бренда ELIZAVECCA нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>7340</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>161</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>бренд ENOUGH есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>344</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>184</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>бренд ENOUGH есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>183</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>бренд ENOUGH есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>183</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>бренд ENOUGH есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>183</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>бренд ENOUGH есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>2435</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>401</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>бренд FARMSTAY есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen Water Full Moist Cream [100g] / Увлажняющий крем с коллагеном</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>484</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>бренд FARMSTAY есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка роллер для глаз</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>232</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>бренд FARMSTAY есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>3493</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>397</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>бренд FARMSTAY есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>901</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>390</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>бренд FARMSTAY есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>JIGOTT - Aloe Real Ampoule Mask [27ml] / Ампульная маска с экстрактом алое</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>1190</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>бренд JIGOTT есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной крем с экстрактом ласточкиного гнезда</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>1614</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>202</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>бренд JIGOTT есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>JIGOTT - Black Snail Real Ampoule Mask [27ml] / Ампульная маска с экстрактом слизи черной улитки</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>1190</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>бренд JIGOTT есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>18</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>JIGOTT - Camellia Real Ampoule Mask [27ml] / Ампульная маска с экстрактом камелии</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>1190</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>бренд JIGOTT есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>19</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>JIGOTT - Caviar Real Ampoule Mask [27ml] / Ампульная маска с экстрактом икры</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>1190</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>бренд JIGOTT есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>20</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>JIGOTT - Collagen Real Ampoule Mask [27ml] / Ампульная маска с коллагеном</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>1190</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>бренд JIGOTT есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>21</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>JIGOTT - Cucumber Real Ampoule Mask [27ml] / Тканевая маска с экстрактом огурца</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>1190</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>бренд JIGOTT есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>22</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>265</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>бренд JIGOTT есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>23</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>JIGOTT - Green Tea Real Ampoule Mask [27ml] / Ампульная маска с экстрактом зеленого чая</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>1190</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>бренд JIGOTT есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>24</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>JIGOTT - Honey Real Ampoule Mask [27ml] / Ампульная маска с экстрактом меда</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>1190</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>бренд JIGOTT есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>25</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>JIGOTT - Hyaluronic Acid Real Ampoule Mask [27ml] / Ампульная маска с гиалуроновой кислотой</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>1190</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>бренд JIGOTT есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>26</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>JIGOTT - Lotus Real Ampoule Mask [27ml] / Ампульная маска с экстрактом лотоса</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>1190</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>бренд JIGOTT есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>27</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml] / Тонер для лица увлажняющий с экстрактом алоэ</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>265</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>бренд JIGOTT есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>28</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>JIGOTT - Pearl Real Ampoule Mask [27ml] / ампульная маска для лица с жемчугом</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>1190</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>бренд JIGOTT есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>29</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>JIGOTT - Placenta Real Ampoule Mask [27ml] / Ампульная маска с плацентой</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>1190</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>бренд JIGOTT есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>30</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>JIGOTT - Pomegranate Real Ampoule Mask [27ml] / Ампульная маска с экстрактом граната</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>1190</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>бренд JIGOTT есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>31</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>JIGOTT - Potato Real Ampoule Mask [27ml] / Ампульная маска с экстрактом картофеля</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>1190</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>бренд JIGOTT есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>32</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>JIGOTT - Red Ginseng Real Ampoule Mask [27ml] / Ампульная маска с красным женьшенем</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>1190</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>бренд JIGOTT есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>33</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>7463</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>202</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>бренд JIGOTT есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>34</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозрастной с муцином улитки</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>186</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>бренд JIGOTT есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>35</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>265</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>бренд JIGOTT есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>36</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>JIGOTT - Vitamin Real Ampoule Mask [27ml] / Ампульная маска с витаминами</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>1190</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>бренд JIGOTT есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>JMSOLUTION</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>37</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>JMSOLUTION  JMSOLUTION - Glory Aqua TOCOPHEROL VITAMIN C MASK PLUS [30ml*10ea] / Тканевая маска</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>450</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>бренда JMSOLUTION нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>38</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - Active Birds Nest Moisture Mask [30ml*10ea] / Ультратонкая тканевая маска с ласточкиным гнездом</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>342</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>бренда JMSOLUTION нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>39</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - Active Golden Caviar Nourishing Mask [30ml*10ea] / Ультратонкая тканевая маска с золотом и икрой</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>342</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>бренда JMSOLUTION нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>40</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - Active Jellyfish Vital Mask [30ml*10ea] / Ультратонкая тканевая маска с экстрактом медузы</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>342</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>бренда JMSOLUTION нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>41</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - MASK PACK DISNEY [30ml*10ea] - ассорти набор из 10шт</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>832</v>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>463</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>бренда JMSOLUTION нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>42</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - The Natural Cordyceps Melitaris Mask Moisture [30ml*10ea] / Тканевая маска для лица с экстрактом кордицепса и комплексом аминокислот</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>318</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>бренда JMSOLUTION нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>43</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - Water Luminous S.O.S. Ringer Mask Black [35ml*10ea] / Ультраувлажняющая тканевая маска</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>450</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>бренда JMSOLUTION нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>44</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>JMSOLUTION ACTIVE BLACK CAVIAR MASK [30ml*10ea] / Ультратонкая тканевая маска с черной икрой</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>342</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>бренда JMSOLUTION нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>45</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>JMSOLUTION GLORY AQUA FULLERENE MASK DELUXE</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>450</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>бренда JMSOLUTION нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>46</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>JMSOLUTION GREEN DEAR TIGER CICA MASK PURE 30ml*10ea / Регенерирующая маска для лица с центеллой</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>342</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>бренда JMSOLUTION нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>47</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>JMSOLUTION PANTHELENE INTENSIVE BARRIER MASK</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>450</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>бренда JMSOLUTION нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n"/>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>LEBELAGE</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="7" t="n"/>
+      <c r="E55" s="5" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>48</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>108</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>бренда LEBELAGE нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n"/>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="7" t="n"/>
+      <c r="E57" s="5" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>49</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>624</v>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>735</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>бренд MANYO есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>50</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и пробиотиками</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>614</v>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>997</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>бренд MANYO есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="n"/>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="n"/>
+      <c r="D60" s="7" t="n"/>
+      <c r="E60" s="5" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>51</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea] / Охлаждающие гидрогелевые патчи для глаз с экстрактом агавы</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>415</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>бренда PETITFEE нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>52</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs] / Охлаждающая гидрогелевая маска для лица с экстрактом агавы</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>486</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>бренда PETITFEE нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>53</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea] / Смягчающие гидрогелевые патчи для глаз с экстрактом артишока</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>415</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>бренда PETITFEE нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>54</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs] / Смягчающая гидрогелевая маска для лица с экстрактом артишока</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D64" s="8" t="n">
+        <v>499</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>бренда PETITFEE нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>55</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="D65" s="8" t="n">
+        <v>591</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>бренда PETITFEE нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>56</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="D66" s="8" t="n">
+        <v>487</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>бренда PETITFEE нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>57</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]/ Гидрогелевые патчи для глаз с черным жемчугом и золотом 1 пара</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>71</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>бренда PETITFEE нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>58</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с черным жемчугом и золотом</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>388</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>бренда PETITFEE нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>59</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с черным жемчугом и золотом</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>478</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>бренда PETITFEE нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>60</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea] / Тонизирующие гидрогелевые патчи для глаз с экстрактом какао</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="D70" s="8" t="n">
+        <v>415</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>бренда PETITFEE нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>61</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs] / Тонизирующая гидрогелевая маска для лица с экстрактом какао</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D71" s="8" t="n">
+        <v>497</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>бренда PETITFEE нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>62</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60ea] / Успокаивающие гидрогелевые патчи для глаз с экстрактом ромашки</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="8" t="n">
+        <v>415</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>бренда PETITFEE нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>63</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с коллагеном и коэнзимом Q10</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>385</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>бренда PETITFEE нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>64</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold &amp; EGF Hydrogel Eye &amp; Spot Patch [60ea]/ гидрогелевые патчи с золотом и EGF</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="8" t="n">
+        <v>385</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>бренда PETITFEE нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>65</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с золотом и улиткой</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="D75" s="8" t="n">
+        <v>415</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>бренда PETITFEE нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>66</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом и экстрактом улитки</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="D76" s="8" t="n">
+        <v>478</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>бренда PETITFEE нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>67</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs] / гидрогелевые патчи для глаз с золотом 1 пара</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>428</v>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>71</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>бренда PETITFEE нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>68</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea] / гидрогелевые патчи для глаз с золотом</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>405</v>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>415</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>бренда PETITFEE нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>69</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="D79" s="8" t="n">
+        <v>507</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>бренда PETITFEE нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>70</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="D80" s="8" t="n">
+        <v>487</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>бренда PETITFEE нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n"/>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>SOME BY MI</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="n"/>
+      <c r="D81" s="7" t="n"/>
+      <c r="E81" s="5" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>71</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D82" s="8" t="n">
+        <v>1057</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>бренд SOME BY MI есть, но этой позиции нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n"/>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>THE ORDINARY</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="n"/>
+      <c r="D83" s="7" t="n"/>
+      <c r="E83" s="5" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>72</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D84" s="8" t="n">
+        <v>845</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>бренда THE ORDINARY нет ни у одного из трех</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr"/>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>55169</v>
+      </c>
+      <c r="D85" s="9" t="inlineStr"/>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>позиций: 72</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4359,32 +7635,131 @@
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr"/>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>29</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>1336</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>1423</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Korea Global</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>1457</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="J38" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>вес не из названия</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>30</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>974</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>1183</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Korshop</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>1217</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>243</v>
+      </c>
+      <c r="J39" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>вес не из названия</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr"/>
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr"/>
-      <c r="D37" s="4" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>позиций: 28</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr"/>
-      <c r="G37" s="4" t="inlineStr"/>
-      <c r="H37" s="4" t="inlineStr"/>
-      <c r="I37" s="4" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr"/>
-      <c r="K37" s="3" t="inlineStr"/>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr"/>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>позиций: 30</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5345,7 +8720,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
